--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24167,53 +24167,96 @@
       <c r="A518" s="1" t="n">
         <v>46277</v>
       </c>
-      <c r="B518" t="n">
+      <c r="B518" s="0" t="n">
         <v>4.3</v>
       </c>
-      <c r="C518" t="n">
+      <c r="C518" s="0" t="n">
         <v>5.3</v>
       </c>
-      <c r="D518" t="n">
+      <c r="D518" s="0" t="n">
         <v>1.6</v>
       </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F518" t="n">
+      <c r="E518" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F518" s="0" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H518" t="n">
+      <c r="G518" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H518" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="I518" t="n">
+      <c r="I518" s="0" t="n">
         <v>7.3</v>
       </c>
-      <c r="J518" t="n">
+      <c r="J518" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="K518" t="n">
+      <c r="K518" s="0" t="n">
         <v>-4.3</v>
       </c>
-      <c r="L518" t="n">
+      <c r="L518" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="M518" t="n">
+      <c r="M518" s="0" t="n">
         <v>-1.2</v>
       </c>
-      <c r="N518" t="n">
+      <c r="N518" s="0" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="1" t="n">
         <v>46278</v>
+      </c>
+      <c r="B519" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C519" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D519" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="I519" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J519" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K519" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="L519" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M519" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="N519" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="520">
@@ -48896,53 +48939,96 @@
       <c r="A518" s="1" t="n">
         <v>46277</v>
       </c>
-      <c r="B518" t="n">
+      <c r="B518" s="0" t="n">
         <v>26.7</v>
       </c>
-      <c r="C518" t="n">
+      <c r="C518" s="0" t="n">
         <v>26.4</v>
       </c>
-      <c r="D518" t="n">
+      <c r="D518" s="0" t="n">
         <v>23.3</v>
       </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F518" t="n">
+      <c r="E518" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F518" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H518" t="n">
+      <c r="G518" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H518" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="I518" t="n">
+      <c r="I518" s="0" t="n">
         <v>26.3</v>
       </c>
-      <c r="J518" t="n">
+      <c r="J518" s="0" t="n">
         <v>21.8</v>
       </c>
-      <c r="K518" t="n">
+      <c r="K518" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="L518" t="n">
+      <c r="L518" s="0" t="n">
         <v>20.7</v>
       </c>
-      <c r="M518" t="n">
+      <c r="M518" s="0" t="n">
         <v>19.4</v>
       </c>
-      <c r="N518" t="n">
+      <c r="N518" s="0" t="n">
         <v>15.4</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="1" t="n">
         <v>46278</v>
+      </c>
+      <c r="B519" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="C519" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D519" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="I519" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J519" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K519" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="L519" t="n">
+        <v>23</v>
+      </c>
+      <c r="M519" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="N519" t="n">
+        <v>18.1</v>
       </c>
     </row>
     <row r="520">
@@ -64589,57 +64675,104 @@
       <c r="A276" s="1" t="n">
         <v>46277</v>
       </c>
-      <c r="B276" t="n">
+      <c r="B276" s="0" t="n">
         <v>15.84</v>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F276" t="n">
+      <c r="C276" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D276" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E276" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F276" s="0" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H276" t="n">
+      <c r="G276" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H276" s="0" t="n">
         <v>10.82</v>
       </c>
-      <c r="I276" t="n">
+      <c r="I276" s="0" t="n">
         <v>16.32</v>
       </c>
-      <c r="J276" t="n">
+      <c r="J276" s="0" t="n">
         <v>12.39</v>
       </c>
-      <c r="K276" t="n">
+      <c r="K276" s="0" t="n">
         <v>9.68</v>
       </c>
-      <c r="L276" t="n">
+      <c r="L276" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="M276" t="n">
+      <c r="M276" s="0" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="N276" t="n">
+      <c r="N276" s="0" t="n">
         <v>10.96</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
         <v>46278</v>
+      </c>
+      <c r="B277" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="I277" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="J277" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="K277" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L277" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="M277" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N277" t="n">
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="278">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24215,47 +24215,47 @@
       <c r="A519" s="1" t="n">
         <v>46278</v>
       </c>
-      <c r="B519" t="n">
+      <c r="B519" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="C519" t="n">
+      <c r="C519" s="0" t="n">
         <v>5.3</v>
       </c>
-      <c r="D519" t="n">
+      <c r="D519" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F519" t="n">
+      <c r="E519" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F519" s="0" t="n">
         <v>-3.8</v>
       </c>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H519" t="n">
+      <c r="G519" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H519" s="0" t="n">
         <v>-3.1</v>
       </c>
-      <c r="I519" t="n">
+      <c r="I519" s="0" t="n">
         <v>7.2</v>
       </c>
-      <c r="J519" t="n">
+      <c r="J519" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="K519" t="n">
+      <c r="K519" s="0" t="n">
         <v>-4.3</v>
       </c>
-      <c r="L519" t="n">
+      <c r="L519" s="0" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M519" t="n">
+      <c r="M519" s="0" t="n">
         <v>-1.8</v>
       </c>
-      <c r="N519" t="n">
+      <c r="N519" s="0" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -24263,10 +24263,96 @@
       <c r="A520" s="1" t="n">
         <v>46279</v>
       </c>
+      <c r="B520" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C520" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D520" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E520" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F520" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G520" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H520" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I520" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J520" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K520" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L520" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="M520" s="0" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="N520" s="0" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="1" t="n">
         <v>46280</v>
+      </c>
+      <c r="B521" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C521" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D521" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F521" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I521" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J521" t="n">
+        <v>2</v>
+      </c>
+      <c r="K521" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="L521" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M521" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N521" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="522">
@@ -48987,47 +49073,47 @@
       <c r="A519" s="1" t="n">
         <v>46278</v>
       </c>
-      <c r="B519" t="n">
+      <c r="B519" s="0" t="n">
         <v>27.9</v>
       </c>
-      <c r="C519" t="n">
+      <c r="C519" s="0" t="n">
         <v>27.8</v>
       </c>
-      <c r="D519" t="n">
+      <c r="D519" s="0" t="n">
         <v>26.3</v>
       </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F519" t="n">
+      <c r="E519" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F519" s="0" t="n">
         <v>20.3</v>
       </c>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H519" t="n">
+      <c r="G519" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H519" s="0" t="n">
         <v>20.9</v>
       </c>
-      <c r="I519" t="n">
+      <c r="I519" s="0" t="n">
         <v>26.4</v>
       </c>
-      <c r="J519" t="n">
+      <c r="J519" s="0" t="n">
         <v>24.2</v>
       </c>
-      <c r="K519" t="n">
+      <c r="K519" s="0" t="n">
         <v>20.8</v>
       </c>
-      <c r="L519" t="n">
+      <c r="L519" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="M519" t="n">
+      <c r="M519" s="0" t="n">
         <v>21.6</v>
       </c>
-      <c r="N519" t="n">
+      <c r="N519" s="0" t="n">
         <v>18.1</v>
       </c>
     </row>
@@ -49035,10 +49121,96 @@
       <c r="A520" s="1" t="n">
         <v>46279</v>
       </c>
+      <c r="B520" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="C520" s="0" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D520" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E520" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F520" s="0" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G520" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H520" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I520" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="J520" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="K520" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L520" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="M520" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N520" s="0" t="n">
+        <v>23.9</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="1" t="n">
         <v>46280</v>
+      </c>
+      <c r="B521" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="C521" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="D521" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F521" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I521" t="n">
+        <v>26</v>
+      </c>
+      <c r="J521" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K521" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="L521" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M521" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="N521" t="n">
+        <v>24.4</v>
       </c>
     </row>
     <row r="522">
@@ -64727,51 +64899,51 @@
       <c r="A277" s="1" t="n">
         <v>46278</v>
       </c>
-      <c r="B277" t="n">
+      <c r="B277" s="0" t="n">
         <v>16.27</v>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F277" t="n">
+      <c r="C277" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D277" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E277" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F277" s="0" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H277" t="n">
+      <c r="G277" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H277" s="0" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="I277" t="n">
+      <c r="I277" s="0" t="n">
         <v>15.76</v>
       </c>
-      <c r="J277" t="n">
+      <c r="J277" s="0" t="n">
         <v>12.84</v>
       </c>
-      <c r="K277" t="n">
+      <c r="K277" s="0" t="n">
         <v>8.5</v>
       </c>
-      <c r="L277" t="n">
+      <c r="L277" s="0" t="n">
         <v>10.7</v>
       </c>
-      <c r="M277" t="n">
+      <c r="M277" s="0" t="n">
         <v>10.2</v>
       </c>
-      <c r="N277" t="n">
+      <c r="N277" s="0" t="n">
         <v>9.140000000000001</v>
       </c>
     </row>
@@ -64779,10 +64951,104 @@
       <c r="A278" s="1" t="n">
         <v>46279</v>
       </c>
+      <c r="B278" s="0" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="C278" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D278" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E278" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F278" s="0" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="G278" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H278" s="0" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="I278" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J278" s="0" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="K278" s="0" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="L278" s="0" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="M278" s="0" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="N278" s="0" t="n">
+        <v>13.54</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
         <v>46280</v>
+      </c>
+      <c r="B279" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="I279" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="J279" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="K279" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="L279" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="M279" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="N279" t="n">
+        <v>14.81</v>
       </c>
     </row>
     <row r="280">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24311,47 +24311,47 @@
       <c r="A521" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="B521" t="n">
+      <c r="B521" s="0" t="n">
         <v>8.5</v>
       </c>
-      <c r="C521" t="n">
+      <c r="C521" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="D521" t="n">
+      <c r="D521" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="E521" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F521" t="n">
+      <c r="E521" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F521" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G521" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H521" t="n">
+      <c r="G521" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H521" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="I521" t="n">
+      <c r="I521" s="0" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J521" t="n">
+      <c r="J521" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K521" t="n">
+      <c r="K521" s="0" t="n">
         <v>-2.8</v>
       </c>
-      <c r="L521" t="n">
+      <c r="L521" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="M521" t="n">
+      <c r="M521" s="0" t="n">
         <v>2.1</v>
       </c>
-      <c r="N521" t="n">
+      <c r="N521" s="0" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -24359,10 +24359,96 @@
       <c r="A522" s="1" t="n">
         <v>46281</v>
       </c>
+      <c r="B522" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C522" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D522" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E522" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F522" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G522" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H522" s="0" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I522" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J522" s="0" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K522" s="0" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L522" s="0" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M522" s="0" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N522" s="0" t="n">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="1" t="n">
         <v>46282</v>
+      </c>
+      <c r="B523" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C523" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D523" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F523" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I523" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J523" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K523" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="L523" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M523" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N523" t="n">
+        <v>10.1</v>
       </c>
     </row>
     <row r="524">
@@ -49169,47 +49255,47 @@
       <c r="A521" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="B521" t="n">
+      <c r="B521" s="0" t="n">
         <v>27.7</v>
       </c>
-      <c r="C521" t="n">
+      <c r="C521" s="0" t="n">
         <v>29.3</v>
       </c>
-      <c r="D521" t="n">
+      <c r="D521" s="0" t="n">
         <v>27.8</v>
       </c>
-      <c r="E521" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F521" t="n">
+      <c r="E521" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F521" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="G521" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H521" t="n">
+      <c r="G521" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H521" s="0" t="n">
         <v>27.5</v>
       </c>
-      <c r="I521" t="n">
+      <c r="I521" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="J521" t="n">
+      <c r="J521" s="0" t="n">
         <v>26.2</v>
       </c>
-      <c r="K521" t="n">
+      <c r="K521" s="0" t="n">
         <v>21.9</v>
       </c>
-      <c r="L521" t="n">
+      <c r="L521" s="0" t="n">
         <v>24.9</v>
       </c>
-      <c r="M521" t="n">
+      <c r="M521" s="0" t="n">
         <v>24.3</v>
       </c>
-      <c r="N521" t="n">
+      <c r="N521" s="0" t="n">
         <v>24.4</v>
       </c>
     </row>
@@ -49217,10 +49303,96 @@
       <c r="A522" s="1" t="n">
         <v>46281</v>
       </c>
+      <c r="B522" s="0" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C522" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="D522" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="E522" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F522" s="0" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="G522" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H522" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I522" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="J522" s="0" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K522" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="L522" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="M522" s="0" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="N522" s="0" t="n">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="1" t="n">
         <v>46282</v>
+      </c>
+      <c r="B523" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="C523" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D523" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F523" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I523" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J523" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="K523" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="L523" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M523" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N523" t="n">
+        <v>21.2</v>
       </c>
     </row>
     <row r="524">
@@ -65003,51 +65175,51 @@
       <c r="A279" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="B279" t="n">
+      <c r="B279" s="0" t="n">
         <v>17.7</v>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F279" t="n">
+      <c r="C279" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D279" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E279" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F279" s="0" t="n">
         <v>9.57</v>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H279" t="n">
+      <c r="G279" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H279" s="0" t="n">
         <v>13.13</v>
       </c>
-      <c r="I279" t="n">
+      <c r="I279" s="0" t="n">
         <v>17.81</v>
       </c>
-      <c r="J279" t="n">
+      <c r="J279" s="0" t="n">
         <v>13.59</v>
       </c>
-      <c r="K279" t="n">
+      <c r="K279" s="0" t="n">
         <v>10.71</v>
       </c>
-      <c r="L279" t="n">
+      <c r="L279" s="0" t="n">
         <v>12.47</v>
       </c>
-      <c r="M279" t="n">
+      <c r="M279" s="0" t="n">
         <v>11.68</v>
       </c>
-      <c r="N279" t="n">
+      <c r="N279" s="0" t="n">
         <v>14.81</v>
       </c>
     </row>
@@ -65055,10 +65227,104 @@
       <c r="A280" s="1" t="n">
         <v>46281</v>
       </c>
+      <c r="B280" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C280" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D280" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E280" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F280" s="0" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="G280" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H280" s="0" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="I280" s="0" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="J280" s="0" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="K280" s="0" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="L280" s="0" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="M280" s="0" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="N280" s="0" t="n">
+        <v>17.49</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
         <v>46282</v>
+      </c>
+      <c r="B281" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I281" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J281" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="K281" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L281" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="M281" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="N281" t="n">
+        <v>14.95</v>
       </c>
     </row>
     <row r="282">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24407,53 +24407,96 @@
       <c r="A523" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B523" t="n">
+      <c r="B523" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="C523" t="n">
+      <c r="C523" s="0" t="n">
         <v>5.8</v>
       </c>
-      <c r="D523" t="n">
+      <c r="D523" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F523" t="n">
+      <c r="E523" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F523" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H523" t="n">
+      <c r="G523" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H523" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="I523" t="n">
+      <c r="I523" s="0" t="n">
         <v>8.1</v>
       </c>
-      <c r="J523" t="n">
+      <c r="J523" s="0" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K523" t="n">
+      <c r="K523" s="0" t="n">
         <v>-1.1</v>
       </c>
-      <c r="L523" t="n">
+      <c r="L523" s="0" t="n">
         <v>1.6</v>
       </c>
-      <c r="M523" t="n">
+      <c r="M523" s="0" t="n">
         <v>-3.9</v>
       </c>
-      <c r="N523" t="n">
+      <c r="N523" s="0" t="n">
         <v>10.1</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="1" t="n">
         <v>46283</v>
+      </c>
+      <c r="B524" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C524" t="n">
+        <v>3</v>
+      </c>
+      <c r="D524" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F524" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I524" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J524" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L524" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M524" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="N524" t="n">
+        <v>8.9</v>
       </c>
     </row>
     <row r="525">
@@ -49351,53 +49394,96 @@
       <c r="A523" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B523" t="n">
+      <c r="B523" s="0" t="n">
         <v>16.2</v>
       </c>
-      <c r="C523" t="n">
+      <c r="C523" s="0" t="n">
         <v>14.7</v>
       </c>
-      <c r="D523" t="n">
+      <c r="D523" s="0" t="n">
         <v>14.8</v>
       </c>
-      <c r="E523" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F523" t="n">
+      <c r="E523" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F523" s="0" t="n">
         <v>15.8</v>
       </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H523" t="n">
+      <c r="G523" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H523" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="I523" t="n">
+      <c r="I523" s="0" t="n">
         <v>19.9</v>
       </c>
-      <c r="J523" t="n">
+      <c r="J523" s="0" t="n">
         <v>15.1</v>
       </c>
-      <c r="K523" t="n">
+      <c r="K523" s="0" t="n">
         <v>13.8</v>
       </c>
-      <c r="L523" t="n">
+      <c r="L523" s="0" t="n">
         <v>15.6</v>
       </c>
-      <c r="M523" t="n">
+      <c r="M523" s="0" t="n">
         <v>14.3</v>
       </c>
-      <c r="N523" t="n">
+      <c r="N523" s="0" t="n">
         <v>21.2</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="1" t="n">
         <v>46283</v>
+      </c>
+      <c r="B524" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="C524" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D524" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F524" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>19</v>
+      </c>
+      <c r="I524" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="J524" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K524" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L524" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M524" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N524" t="n">
+        <v>14.6</v>
       </c>
     </row>
     <row r="525">
@@ -65279,57 +65365,104 @@
       <c r="A281" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B281" t="n">
+      <c r="B281" s="0" t="n">
         <v>9.99</v>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F281" t="n">
+      <c r="C281" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D281" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E281" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F281" s="0" t="n">
         <v>9.81</v>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H281" t="n">
+      <c r="G281" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H281" s="0" t="n">
         <v>14.75</v>
       </c>
-      <c r="I281" t="n">
+      <c r="I281" s="0" t="n">
         <v>12.5</v>
       </c>
-      <c r="J281" t="n">
+      <c r="J281" s="0" t="n">
         <v>8.06</v>
       </c>
-      <c r="K281" t="n">
+      <c r="K281" s="0" t="n">
         <v>6.25</v>
       </c>
-      <c r="L281" t="n">
+      <c r="L281" s="0" t="n">
         <v>8.460000000000001</v>
       </c>
-      <c r="M281" t="n">
+      <c r="M281" s="0" t="n">
         <v>5.16</v>
       </c>
-      <c r="N281" t="n">
+      <c r="N281" s="0" t="n">
         <v>14.95</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
         <v>46283</v>
+      </c>
+      <c r="B282" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="I282" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="J282" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="K282" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="L282" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="M282" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="N282" t="n">
+        <v>11.21</v>
       </c>
     </row>
     <row r="283">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24455,53 +24455,96 @@
       <c r="A524" s="1" t="n">
         <v>46283</v>
       </c>
-      <c r="B524" t="n">
+      <c r="B524" s="0" t="n">
         <v>3.7</v>
       </c>
-      <c r="C524" t="n">
+      <c r="C524" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D524" t="n">
+      <c r="D524" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F524" t="n">
+      <c r="E524" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F524" s="0" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H524" t="n">
+      <c r="G524" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H524" s="0" t="n">
         <v>3.3</v>
       </c>
-      <c r="I524" t="n">
+      <c r="I524" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="J524" t="n">
+      <c r="J524" s="0" t="n">
         <v>-1.2</v>
       </c>
-      <c r="K524" t="n">
+      <c r="K524" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="L524" t="n">
+      <c r="L524" s="0" t="n">
         <v>3.2</v>
       </c>
-      <c r="M524" t="n">
+      <c r="M524" s="0" t="n">
         <v>-3.1</v>
       </c>
-      <c r="N524" t="n">
+      <c r="N524" s="0" t="n">
         <v>8.9</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="1" t="n">
         <v>46284</v>
+      </c>
+      <c r="B525" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C525" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D525" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F525" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I525" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J525" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="K525" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="L525" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="M525" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="N525" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="526">
@@ -49442,53 +49485,96 @@
       <c r="A524" s="1" t="n">
         <v>46283</v>
       </c>
-      <c r="B524" t="n">
+      <c r="B524" s="0" t="n">
         <v>19.7</v>
       </c>
-      <c r="C524" t="n">
+      <c r="C524" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="D524" t="n">
+      <c r="D524" s="0" t="n">
         <v>16.5</v>
       </c>
-      <c r="E524" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F524" t="n">
+      <c r="E524" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F524" s="0" t="n">
         <v>13.5</v>
       </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H524" t="n">
+      <c r="G524" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H524" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="I524" t="n">
+      <c r="I524" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="J524" t="n">
+      <c r="J524" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="K524" t="n">
+      <c r="K524" s="0" t="n">
         <v>11.4</v>
       </c>
-      <c r="L524" t="n">
+      <c r="L524" s="0" t="n">
         <v>12.7</v>
       </c>
-      <c r="M524" t="n">
+      <c r="M524" s="0" t="n">
         <v>12.8</v>
       </c>
-      <c r="N524" t="n">
+      <c r="N524" s="0" t="n">
         <v>14.6</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="1" t="n">
         <v>46284</v>
+      </c>
+      <c r="B525" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C525" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D525" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F525" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I525" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J525" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="K525" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L525" t="n">
+        <v>18</v>
+      </c>
+      <c r="M525" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N525" t="n">
+        <v>17.5</v>
       </c>
     </row>
     <row r="526">
@@ -65417,57 +65503,104 @@
       <c r="A282" s="1" t="n">
         <v>46283</v>
       </c>
-      <c r="B282" t="n">
+      <c r="B282" s="0" t="n">
         <v>11.4</v>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F282" t="n">
+      <c r="C282" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D282" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E282" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F282" s="0" t="n">
         <v>5.29</v>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H282" t="n">
+      <c r="G282" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H282" s="0" t="n">
         <v>10.69</v>
       </c>
-      <c r="I282" t="n">
+      <c r="I282" s="0" t="n">
         <v>10.69</v>
       </c>
-      <c r="J282" t="n">
+      <c r="J282" s="0" t="n">
         <v>8.16</v>
       </c>
-      <c r="K282" t="n">
+      <c r="K282" s="0" t="n">
         <v>5.59</v>
       </c>
-      <c r="L282" t="n">
+      <c r="L282" s="0" t="n">
         <v>7.33</v>
       </c>
-      <c r="M282" t="n">
+      <c r="M282" s="0" t="n">
         <v>5.36</v>
       </c>
-      <c r="N282" t="n">
+      <c r="N282" s="0" t="n">
         <v>11.21</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
         <v>46284</v>
+      </c>
+      <c r="B283" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I283" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="J283" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="K283" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="L283" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="M283" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="N283" t="n">
+        <v>10.03</v>
       </c>
     </row>
     <row r="284">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24503,53 +24503,96 @@
       <c r="A525" s="1" t="n">
         <v>46284</v>
       </c>
-      <c r="B525" t="n">
+      <c r="B525" s="0" t="n">
         <v>8.1</v>
       </c>
-      <c r="C525" t="n">
+      <c r="C525" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="D525" t="n">
+      <c r="D525" s="0" t="n">
         <v>2.2</v>
       </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F525" t="n">
+      <c r="E525" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F525" s="0" t="n">
         <v>-6.7</v>
       </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H525" t="n">
+      <c r="G525" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H525" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="I525" t="n">
+      <c r="I525" s="0" t="n">
         <v>5.2</v>
       </c>
-      <c r="J525" t="n">
+      <c r="J525" s="0" t="n">
         <v>-1.2</v>
       </c>
-      <c r="K525" t="n">
+      <c r="K525" s="0" t="n">
         <v>-6.6</v>
       </c>
-      <c r="L525" t="n">
+      <c r="L525" s="0" t="n">
         <v>-2.1</v>
       </c>
-      <c r="M525" t="n">
+      <c r="M525" s="0" t="n">
         <v>-1.9</v>
       </c>
-      <c r="N525" t="n">
+      <c r="N525" s="0" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="n">
         <v>46285</v>
+      </c>
+      <c r="B526" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C526" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I526" t="n">
+        <v>5</v>
+      </c>
+      <c r="J526" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K526" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="L526" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="M526" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="N526" t="n">
+        <v>5.7</v>
       </c>
     </row>
     <row r="527">
@@ -49533,53 +49576,96 @@
       <c r="A525" s="1" t="n">
         <v>46284</v>
       </c>
-      <c r="B525" t="n">
+      <c r="B525" s="0" t="n">
         <v>22.7</v>
       </c>
-      <c r="C525" t="n">
+      <c r="C525" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="D525" t="n">
+      <c r="D525" s="0" t="n">
         <v>21.8</v>
       </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F525" t="n">
+      <c r="E525" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F525" s="0" t="n">
         <v>16.5</v>
       </c>
-      <c r="G525" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H525" t="n">
+      <c r="G525" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H525" s="0" t="n">
         <v>21.1</v>
       </c>
-      <c r="I525" t="n">
+      <c r="I525" s="0" t="n">
         <v>19.7</v>
       </c>
-      <c r="J525" t="n">
+      <c r="J525" s="0" t="n">
         <v>19.8</v>
       </c>
-      <c r="K525" t="n">
+      <c r="K525" s="0" t="n">
         <v>15.7</v>
       </c>
-      <c r="L525" t="n">
+      <c r="L525" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="M525" t="n">
+      <c r="M525" s="0" t="n">
         <v>10.2</v>
       </c>
-      <c r="N525" t="n">
+      <c r="N525" s="0" t="n">
         <v>17.5</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="n">
         <v>46285</v>
+      </c>
+      <c r="B526" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="C526" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D526" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I526" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J526" t="n">
+        <v>21</v>
+      </c>
+      <c r="K526" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L526" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M526" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N526" t="n">
+        <v>20.7</v>
       </c>
     </row>
     <row r="527">
@@ -65555,57 +65641,104 @@
       <c r="A283" s="1" t="n">
         <v>46284</v>
       </c>
-      <c r="B283" t="n">
+      <c r="B283" s="0" t="n">
         <v>13.64</v>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F283" t="n">
+      <c r="C283" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D283" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E283" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F283" s="0" t="n">
         <v>4.65</v>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H283" t="n">
+      <c r="G283" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H283" s="0" t="n">
         <v>11.25</v>
       </c>
-      <c r="I283" t="n">
+      <c r="I283" s="0" t="n">
         <v>12.19</v>
       </c>
-      <c r="J283" t="n">
+      <c r="J283" s="0" t="n">
         <v>9.09</v>
       </c>
-      <c r="K283" t="n">
+      <c r="K283" s="0" t="n">
         <v>5.61</v>
       </c>
-      <c r="L283" t="n">
+      <c r="L283" s="0" t="n">
         <v>7.01</v>
       </c>
-      <c r="M283" t="n">
+      <c r="M283" s="0" t="n">
         <v>5.09</v>
       </c>
-      <c r="N283" t="n">
+      <c r="N283" s="0" t="n">
         <v>10.03</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
         <v>46285</v>
+      </c>
+      <c r="B284" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="I284" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="J284" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="K284" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="L284" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="M284" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="N284" t="n">
+        <v>12.7</v>
       </c>
     </row>
     <row r="285">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24551,53 +24551,96 @@
       <c r="A526" s="1" t="n">
         <v>46285</v>
       </c>
-      <c r="B526" t="n">
+      <c r="B526" s="0" t="n">
         <v>3.2</v>
       </c>
-      <c r="C526" t="n">
+      <c r="C526" s="0" t="n">
         <v>2.9</v>
       </c>
-      <c r="D526" t="n">
+      <c r="D526" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F526" t="n">
+      <c r="E526" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F526" s="0" t="n">
         <v>-6.3</v>
       </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H526" t="n">
+      <c r="G526" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H526" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="I526" t="n">
+      <c r="I526" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J526" t="n">
+      <c r="J526" s="0" t="n">
         <v>-2.5</v>
       </c>
-      <c r="K526" t="n">
+      <c r="K526" s="0" t="n">
         <v>-5.9</v>
       </c>
-      <c r="L526" t="n">
+      <c r="L526" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="M526" t="n">
+      <c r="M526" s="0" t="n">
         <v>-3.6</v>
       </c>
-      <c r="N526" t="n">
+      <c r="N526" s="0" t="n">
         <v>5.7</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="1" t="n">
         <v>46286</v>
+      </c>
+      <c r="B527" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C527" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D527" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F527" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I527" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J527" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K527" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="L527" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M527" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="N527" t="n">
+        <v>7.3</v>
       </c>
     </row>
     <row r="528">
@@ -49624,53 +49667,96 @@
       <c r="A526" s="1" t="n">
         <v>46285</v>
       </c>
-      <c r="B526" t="n">
+      <c r="B526" s="0" t="n">
         <v>21.8</v>
       </c>
-      <c r="C526" t="n">
+      <c r="C526" s="0" t="n">
         <v>21.9</v>
       </c>
-      <c r="D526" t="n">
+      <c r="D526" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F526" t="n">
+      <c r="E526" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F526" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H526" t="n">
+      <c r="G526" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H526" s="0" t="n">
         <v>20.1</v>
       </c>
-      <c r="I526" t="n">
+      <c r="I526" s="0" t="n">
         <v>21.5</v>
       </c>
-      <c r="J526" t="n">
+      <c r="J526" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="K526" t="n">
+      <c r="K526" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="L526" t="n">
+      <c r="L526" s="0" t="n">
         <v>21.1</v>
       </c>
-      <c r="M526" t="n">
+      <c r="M526" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="N526" t="n">
+      <c r="N526" s="0" t="n">
         <v>20.7</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="1" t="n">
         <v>46286</v>
+      </c>
+      <c r="B527" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C527" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D527" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F527" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I527" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J527" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="K527" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L527" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M527" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="N527" t="n">
+        <v>22.1</v>
       </c>
     </row>
     <row r="528">
@@ -65693,57 +65779,104 @@
       <c r="A284" s="1" t="n">
         <v>46285</v>
       </c>
-      <c r="B284" t="n">
+      <c r="B284" s="0" t="n">
         <v>12.39</v>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F284" t="n">
+      <c r="C284" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D284" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E284" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F284" s="0" t="n">
         <v>6.19</v>
       </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H284" t="n">
+      <c r="G284" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H284" s="0" t="n">
         <v>12.34</v>
       </c>
-      <c r="I284" t="n">
+      <c r="I284" s="0" t="n">
         <v>12.25</v>
       </c>
-      <c r="J284" t="n">
+      <c r="J284" s="0" t="n">
         <v>9.35</v>
       </c>
-      <c r="K284" t="n">
+      <c r="K284" s="0" t="n">
         <v>7.06</v>
       </c>
-      <c r="L284" t="n">
+      <c r="L284" s="0" t="n">
         <v>8.42</v>
       </c>
-      <c r="M284" t="n">
+      <c r="M284" s="0" t="n">
         <v>6.79</v>
       </c>
-      <c r="N284" t="n">
+      <c r="N284" s="0" t="n">
         <v>12.7</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
         <v>46286</v>
+      </c>
+      <c r="B285" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="I285" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="J285" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="K285" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="L285" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M285" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="N285" t="n">
+        <v>13.86</v>
       </c>
     </row>
     <row r="286">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24599,47 +24599,47 @@
       <c r="A527" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="B527" t="n">
+      <c r="B527" s="0" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="C527" t="n">
+      <c r="C527" s="0" t="n">
         <v>4.2</v>
       </c>
-      <c r="D527" t="n">
+      <c r="D527" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="E527" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F527" t="n">
+      <c r="E527" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F527" s="0" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H527" t="n">
+      <c r="G527" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H527" s="0" t="n">
         <v>2.6</v>
       </c>
-      <c r="I527" t="n">
+      <c r="I527" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="J527" t="n">
+      <c r="J527" s="0" t="n">
         <v>-0.9</v>
       </c>
-      <c r="K527" t="n">
+      <c r="K527" s="0" t="n">
         <v>-5.2</v>
       </c>
-      <c r="L527" t="n">
+      <c r="L527" s="0" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M527" t="n">
+      <c r="M527" s="0" t="n">
         <v>-2.3</v>
       </c>
-      <c r="N527" t="n">
+      <c r="N527" s="0" t="n">
         <v>7.3</v>
       </c>
     </row>
@@ -24647,10 +24647,96 @@
       <c r="A528" s="1" t="n">
         <v>46287</v>
       </c>
+      <c r="B528" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C528" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D528" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E528" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F528" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G528" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H528" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I528" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J528" s="0" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K528" s="0" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="L528" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="M528" s="0" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="N528" s="0" t="n">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="1" t="n">
         <v>46288</v>
+      </c>
+      <c r="B529" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C529" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D529" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F529" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I529" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J529" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K529" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L529" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M529" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N529" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="530">
@@ -49715,47 +49801,47 @@
       <c r="A527" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="B527" t="n">
+      <c r="B527" s="0" t="n">
         <v>22.6</v>
       </c>
-      <c r="C527" t="n">
+      <c r="C527" s="0" t="n">
         <v>21.5</v>
       </c>
-      <c r="D527" t="n">
+      <c r="D527" s="0" t="n">
         <v>17.6</v>
       </c>
-      <c r="E527" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F527" t="n">
+      <c r="E527" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F527" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H527" t="n">
+      <c r="G527" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H527" s="0" t="n">
         <v>20.4</v>
       </c>
-      <c r="I527" t="n">
+      <c r="I527" s="0" t="n">
         <v>22.6</v>
       </c>
-      <c r="J527" t="n">
+      <c r="J527" s="0" t="n">
         <v>17.9</v>
       </c>
-      <c r="K527" t="n">
+      <c r="K527" s="0" t="n">
         <v>17.1</v>
       </c>
-      <c r="L527" t="n">
+      <c r="L527" s="0" t="n">
         <v>20.1</v>
       </c>
-      <c r="M527" t="n">
+      <c r="M527" s="0" t="n">
         <v>12.6</v>
       </c>
-      <c r="N527" t="n">
+      <c r="N527" s="0" t="n">
         <v>22.1</v>
       </c>
     </row>
@@ -49763,10 +49849,96 @@
       <c r="A528" s="1" t="n">
         <v>46287</v>
       </c>
+      <c r="B528" s="0" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C528" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D528" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="E528" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F528" s="0" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G528" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H528" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I528" s="0" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J528" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K528" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="L528" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="M528" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="N528" s="0" t="n">
+        <v>16.5</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="1" t="n">
         <v>46288</v>
+      </c>
+      <c r="B529" t="n">
+        <v>19</v>
+      </c>
+      <c r="C529" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D529" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F529" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I529" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J529" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K529" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L529" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M529" t="n">
+        <v>13</v>
+      </c>
+      <c r="N529" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="530">
@@ -65831,51 +66003,51 @@
       <c r="A285" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="B285" t="n">
+      <c r="B285" s="0" t="n">
         <v>13.22</v>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F285" t="n">
+      <c r="C285" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D285" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E285" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F285" s="0" t="n">
         <v>6.39</v>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H285" t="n">
+      <c r="G285" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H285" s="0" t="n">
         <v>11.03</v>
       </c>
-      <c r="I285" t="n">
+      <c r="I285" s="0" t="n">
         <v>14.43</v>
       </c>
-      <c r="J285" t="n">
+      <c r="J285" s="0" t="n">
         <v>9.08</v>
       </c>
-      <c r="K285" t="n">
+      <c r="K285" s="0" t="n">
         <v>7.36</v>
       </c>
-      <c r="L285" t="n">
+      <c r="L285" s="0" t="n">
         <v>9.51</v>
       </c>
-      <c r="M285" t="n">
+      <c r="M285" s="0" t="n">
         <v>5.26</v>
       </c>
-      <c r="N285" t="n">
+      <c r="N285" s="0" t="n">
         <v>13.86</v>
       </c>
     </row>
@@ -65883,10 +66055,104 @@
       <c r="A286" s="1" t="n">
         <v>46287</v>
       </c>
+      <c r="B286" s="0" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="C286" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D286" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E286" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F286" s="0" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="G286" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H286" s="0" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="I286" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J286" s="0" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="K286" s="0" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L286" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M286" s="0" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N286" s="0" t="n">
+        <v>11.49</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
         <v>46288</v>
+      </c>
+      <c r="B287" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="I287" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="J287" t="n">
+        <v>8</v>
+      </c>
+      <c r="K287" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="L287" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="M287" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="N287" t="n">
+        <v>7.6</v>
       </c>
     </row>
     <row r="288">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24695,53 +24695,96 @@
       <c r="A529" s="1" t="n">
         <v>46288</v>
       </c>
-      <c r="B529" t="n">
+      <c r="B529" s="0" t="n">
         <v>3.5</v>
       </c>
-      <c r="C529" t="n">
+      <c r="C529" s="0" t="n">
         <v>3.8</v>
       </c>
-      <c r="D529" t="n">
+      <c r="D529" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F529" t="n">
+      <c r="E529" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F529" s="0" t="n">
         <v>3.4</v>
       </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H529" t="n">
+      <c r="G529" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H529" s="0" t="n">
         <v>2.9</v>
       </c>
-      <c r="I529" t="n">
+      <c r="I529" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="J529" t="n">
+      <c r="J529" s="0" t="n">
         <v>-1.3</v>
       </c>
-      <c r="K529" t="n">
+      <c r="K529" s="0" t="n">
         <v>-1.9</v>
       </c>
-      <c r="L529" t="n">
+      <c r="L529" s="0" t="n">
         <v>3.1</v>
       </c>
-      <c r="M529" t="n">
+      <c r="M529" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="N529" t="n">
+      <c r="N529" s="0" t="n">
         <v>4.4</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="1" t="n">
         <v>46289</v>
+      </c>
+      <c r="B530" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C530" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D530" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F530" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I530" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J530" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K530" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="L530" t="n">
+        <v>3</v>
+      </c>
+      <c r="M530" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N530" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="531">
@@ -49897,53 +49940,96 @@
       <c r="A529" s="1" t="n">
         <v>46288</v>
       </c>
-      <c r="B529" t="n">
+      <c r="B529" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="C529" t="n">
+      <c r="C529" s="0" t="n">
         <v>17.4</v>
       </c>
-      <c r="D529" t="n">
+      <c r="D529" s="0" t="n">
         <v>17.4</v>
       </c>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F529" t="n">
+      <c r="E529" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F529" s="0" t="n">
         <v>11.8</v>
       </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H529" t="n">
+      <c r="G529" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H529" s="0" t="n">
         <v>14.8</v>
       </c>
-      <c r="I529" t="n">
+      <c r="I529" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="J529" t="n">
+      <c r="J529" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="K529" t="n">
+      <c r="K529" s="0" t="n">
         <v>12.9</v>
       </c>
-      <c r="L529" t="n">
+      <c r="L529" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="M529" t="n">
+      <c r="M529" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="N529" t="n">
+      <c r="N529" s="0" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="1" t="n">
         <v>46289</v>
+      </c>
+      <c r="B530" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C530" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D530" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F530" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I530" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J530" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K530" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="L530" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M530" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N530" t="n">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="531">
@@ -66107,57 +66193,104 @@
       <c r="A287" s="1" t="n">
         <v>46288</v>
       </c>
-      <c r="B287" t="n">
+      <c r="B287" s="0" t="n">
         <v>11.16</v>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F287" t="n">
+      <c r="C287" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D287" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E287" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F287" s="0" t="n">
         <v>4.95</v>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H287" t="n">
+      <c r="G287" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H287" s="0" t="n">
         <v>8.359999999999999</v>
       </c>
-      <c r="I287" t="n">
+      <c r="I287" s="0" t="n">
         <v>11.33</v>
       </c>
-      <c r="J287" t="n">
+      <c r="J287" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K287" t="n">
+      <c r="K287" s="0" t="n">
         <v>5.32</v>
       </c>
-      <c r="L287" t="n">
+      <c r="L287" s="0" t="n">
         <v>7.74</v>
       </c>
-      <c r="M287" t="n">
+      <c r="M287" s="0" t="n">
         <v>5.95</v>
       </c>
-      <c r="N287" t="n">
+      <c r="N287" s="0" t="n">
         <v>7.6</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
         <v>46289</v>
+      </c>
+      <c r="B288" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="I288" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="J288" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="K288" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="L288" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="M288" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="N288" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="289">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24743,47 +24743,47 @@
       <c r="A530" s="1" t="n">
         <v>46289</v>
       </c>
-      <c r="B530" t="n">
+      <c r="B530" s="0" t="n">
         <v>6.4</v>
       </c>
-      <c r="C530" t="n">
+      <c r="C530" s="0" t="n">
         <v>7.8</v>
       </c>
-      <c r="D530" t="n">
+      <c r="D530" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F530" t="n">
+      <c r="E530" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F530" s="0" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G530" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H530" t="n">
+      <c r="G530" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H530" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I530" t="n">
+      <c r="I530" s="0" t="n">
         <v>6.3</v>
       </c>
-      <c r="J530" t="n">
+      <c r="J530" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="K530" t="n">
+      <c r="K530" s="0" t="n">
         <v>-3.4</v>
       </c>
-      <c r="L530" t="n">
+      <c r="L530" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M530" t="n">
+      <c r="M530" s="0" t="n">
         <v>2.2</v>
       </c>
-      <c r="N530" t="n">
+      <c r="N530" s="0" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -24791,20 +24791,192 @@
       <c r="A531" s="1" t="n">
         <v>46290</v>
       </c>
+      <c r="B531" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C531" s="0" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D531" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E531" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F531" s="0" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G531" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H531" s="0" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I531" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J531" s="0" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K531" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L531" s="0" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M531" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="N531" s="0" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="1" t="n">
         <v>46291</v>
       </c>
+      <c r="B532" s="0" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C532" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D532" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E532" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F532" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G532" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H532" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I532" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J532" s="0" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="K532" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="L532" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M532" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="N532" s="0" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="1" t="n">
         <v>46292</v>
       </c>
+      <c r="B533" s="0" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C533" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D533" s="0" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="E533" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F533" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="G533" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H533" s="0" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I533" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J533" s="0" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="K533" s="0" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="L533" s="0" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="M533" s="0" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="N533" s="0" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="1" t="n">
         <v>46293</v>
+      </c>
+      <c r="B534" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C534" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="D534" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F534" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I534" t="n">
+        <v>3</v>
+      </c>
+      <c r="J534" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="K534" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="L534" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="M534" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="N534" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -49988,47 +50160,47 @@
       <c r="A530" s="1" t="n">
         <v>46289</v>
       </c>
-      <c r="B530" t="n">
+      <c r="B530" s="0" t="n">
         <v>19.8</v>
       </c>
-      <c r="C530" t="n">
+      <c r="C530" s="0" t="n">
         <v>16.7</v>
       </c>
-      <c r="D530" t="n">
+      <c r="D530" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F530" t="n">
+      <c r="E530" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F530" s="0" t="n">
         <v>12.7</v>
       </c>
-      <c r="G530" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H530" t="n">
+      <c r="G530" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H530" s="0" t="n">
         <v>17.4</v>
       </c>
-      <c r="I530" t="n">
+      <c r="I530" s="0" t="n">
         <v>15.9</v>
       </c>
-      <c r="J530" t="n">
+      <c r="J530" s="0" t="n">
         <v>22.9</v>
       </c>
-      <c r="K530" t="n">
+      <c r="K530" s="0" t="n">
         <v>13.7</v>
       </c>
-      <c r="L530" t="n">
+      <c r="L530" s="0" t="n">
         <v>15.9</v>
       </c>
-      <c r="M530" t="n">
+      <c r="M530" s="0" t="n">
         <v>12.2</v>
       </c>
-      <c r="N530" t="n">
+      <c r="N530" s="0" t="n">
         <v>8.800000000000001</v>
       </c>
     </row>
@@ -50036,20 +50208,192 @@
       <c r="A531" s="1" t="n">
         <v>46290</v>
       </c>
+      <c r="B531" s="0" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C531" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D531" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E531" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F531" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G531" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H531" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I531" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J531" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K531" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L531" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M531" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="N531" s="0" t="n">
+        <v>11.4</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="1" t="n">
         <v>46291</v>
       </c>
+      <c r="B532" s="0" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="C532" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D532" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E532" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F532" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G532" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H532" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I532" s="0" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J532" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="K532" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L532" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M532" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N532" s="0" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="1" t="n">
         <v>46292</v>
       </c>
+      <c r="B533" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C533" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D533" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E533" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F533" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G533" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H533" s="0" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="I533" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J533" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K533" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L533" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M533" s="0" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N533" s="0" t="n">
+        <v>14.4</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="1" t="n">
         <v>46293</v>
+      </c>
+      <c r="B534" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C534" t="n">
+        <v>8</v>
+      </c>
+      <c r="D534" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F534" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I534" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J534" t="n">
+        <v>4</v>
+      </c>
+      <c r="K534" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L534" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M534" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N534" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="535">
@@ -66245,51 +66589,51 @@
       <c r="A288" s="1" t="n">
         <v>46289</v>
       </c>
-      <c r="B288" t="n">
+      <c r="B288" s="0" t="n">
         <v>12.08</v>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F288" t="n">
+      <c r="C288" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D288" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E288" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F288" s="0" t="n">
         <v>4.71</v>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H288" t="n">
+      <c r="G288" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H288" s="0" t="n">
         <v>7.51</v>
       </c>
-      <c r="I288" t="n">
+      <c r="I288" s="0" t="n">
         <v>10.63</v>
       </c>
-      <c r="J288" t="n">
+      <c r="J288" s="0" t="n">
         <v>7.68</v>
       </c>
-      <c r="K288" t="n">
+      <c r="K288" s="0" t="n">
         <v>4.99</v>
       </c>
-      <c r="L288" t="n">
+      <c r="L288" s="0" t="n">
         <v>8.24</v>
       </c>
-      <c r="M288" t="n">
+      <c r="M288" s="0" t="n">
         <v>6.29</v>
       </c>
-      <c r="N288" t="n">
+      <c r="N288" s="0" t="n">
         <v>6.25</v>
       </c>
     </row>
@@ -66297,20 +66641,208 @@
       <c r="A289" s="1" t="n">
         <v>46290</v>
       </c>
+      <c r="B289" s="0" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="C289" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D289" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E289" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F289" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G289" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H289" s="0" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="I289" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J289" s="0" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="K289" s="0" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="L289" s="0" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="M289" s="0" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="N289" s="0" t="n">
+        <v>8.359999999999999</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
         <v>46291</v>
       </c>
+      <c r="B290" s="0" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="C290" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D290" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E290" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F290" s="0" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G290" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H290" s="0" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="I290" s="0" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="J290" s="0" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="K290" s="0" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L290" s="0" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="M290" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N290" s="0" t="n">
+        <v>9.15</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
         <v>46292</v>
       </c>
+      <c r="B291" s="0" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="C291" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D291" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E291" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F291" s="0" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="G291" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H291" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I291" s="0" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="J291" s="0" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K291" s="0" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="L291" s="0" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M291" s="0" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="N291" s="0" t="n">
+        <v>6.61</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
         <v>46293</v>
+      </c>
+      <c r="B292" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I292" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J292" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="K292" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="L292" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M292" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="N292" t="n">
+        <v>3.04</v>
       </c>
     </row>
     <row r="293">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24935,53 +24935,96 @@
       <c r="A534" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="B534" t="n">
+      <c r="B534" s="0" t="n">
         <v>-1.4</v>
       </c>
-      <c r="C534" t="n">
+      <c r="C534" s="0" t="n">
         <v>-2.1</v>
       </c>
-      <c r="D534" t="n">
+      <c r="D534" s="0" t="n">
         <v>-6.3</v>
       </c>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F534" t="n">
+      <c r="E534" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F534" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H534" t="n">
+      <c r="G534" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H534" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="I534" t="n">
+      <c r="I534" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J534" t="n">
+      <c r="J534" s="0" t="n">
         <v>-8.1</v>
       </c>
-      <c r="K534" t="n">
+      <c r="K534" s="0" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="L534" t="n">
+      <c r="L534" s="0" t="n">
         <v>-3.8</v>
       </c>
-      <c r="M534" t="n">
+      <c r="M534" s="0" t="n">
         <v>-6.8</v>
       </c>
-      <c r="N534" t="n">
+      <c r="N534" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="1" t="n">
         <v>46294</v>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C535" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D535" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F535" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="I535" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="J535" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K535" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="L535" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="M535" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="N535" t="n">
+        <v>-5</v>
       </c>
     </row>
     <row r="536">
@@ -50352,53 +50395,96 @@
       <c r="A534" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="B534" t="n">
+      <c r="B534" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="C534" t="n">
+      <c r="C534" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D534" t="n">
+      <c r="D534" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F534" t="n">
+      <c r="E534" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F534" s="0" t="n">
         <v>7.8</v>
       </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H534" t="n">
+      <c r="G534" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H534" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="I534" t="n">
+      <c r="I534" s="0" t="n">
         <v>11.1</v>
       </c>
-      <c r="J534" t="n">
+      <c r="J534" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K534" t="n">
+      <c r="K534" s="0" t="n">
         <v>0.9</v>
       </c>
-      <c r="L534" t="n">
+      <c r="L534" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="M534" t="n">
+      <c r="M534" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="N534" t="n">
+      <c r="N534" s="0" t="n">
         <v>9.5</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="1" t="n">
         <v>46294</v>
+      </c>
+      <c r="B535" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C535" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D535" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F535" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I535" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J535" t="n">
+        <v>4</v>
+      </c>
+      <c r="K535" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L535" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M535" t="n">
+        <v>2</v>
+      </c>
+      <c r="N535" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="536">
@@ -66797,57 +66883,104 @@
       <c r="A292" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="B292" t="n">
+      <c r="B292" s="0" t="n">
         <v>4.26</v>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F292" t="n">
+      <c r="C292" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D292" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E292" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F292" s="0" t="n">
         <v>-0.29</v>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H292" t="n">
+      <c r="G292" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H292" s="0" t="n">
         <v>4.15</v>
       </c>
-      <c r="I292" t="n">
+      <c r="I292" s="0" t="n">
         <v>6.7</v>
       </c>
-      <c r="J292" t="n">
+      <c r="J292" s="0" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="K292" t="n">
+      <c r="K292" s="0" t="n">
         <v>-2.92</v>
       </c>
-      <c r="L292" t="n">
+      <c r="L292" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="M292" t="n">
+      <c r="M292" s="0" t="n">
         <v>-2.76</v>
       </c>
-      <c r="N292" t="n">
+      <c r="N292" s="0" t="n">
         <v>3.04</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
         <v>46294</v>
+      </c>
+      <c r="B293" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I293" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="L293" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="M293" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="N293" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="294">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24983,53 +24983,96 @@
       <c r="A535" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="B535" t="n">
+      <c r="B535" s="0" t="n">
         <v>-0.4</v>
       </c>
-      <c r="C535" t="n">
+      <c r="C535" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="D535" t="n">
+      <c r="D535" s="0" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F535" t="n">
+      <c r="E535" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F535" s="0" t="n">
         <v>-7.9</v>
       </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H535" t="n">
+      <c r="G535" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H535" s="0" t="n">
         <v>-4.3</v>
       </c>
-      <c r="I535" t="n">
+      <c r="I535" s="0" t="n">
         <v>-3.6</v>
       </c>
-      <c r="J535" t="n">
+      <c r="J535" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="K535" t="n">
+      <c r="K535" s="0" t="n">
         <v>-10.3</v>
       </c>
-      <c r="L535" t="n">
+      <c r="L535" s="0" t="n">
         <v>-3.9</v>
       </c>
-      <c r="M535" t="n">
+      <c r="M535" s="0" t="n">
         <v>-9.9</v>
       </c>
-      <c r="N535" t="n">
+      <c r="N535" s="0" t="n">
         <v>-5</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="1" t="n">
         <v>46295</v>
+      </c>
+      <c r="B536" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="C536" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="D536" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F536" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I536" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="J536" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="K536" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="L536" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="M536" t="n">
+        <v>-9</v>
+      </c>
+      <c r="N536" t="n">
+        <v>-3.9</v>
       </c>
     </row>
     <row r="537">
@@ -50443,53 +50486,96 @@
       <c r="A535" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="B535" t="n">
+      <c r="B535" s="0" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="C535" t="n">
+      <c r="C535" s="0" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D535" t="n">
+      <c r="D535" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F535" t="n">
+      <c r="E535" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F535" s="0" t="n">
         <v>0.9</v>
       </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H535" t="n">
+      <c r="G535" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H535" s="0" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I535" t="n">
+      <c r="I535" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="J535" t="n">
+      <c r="J535" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K535" t="n">
+      <c r="K535" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="L535" t="n">
+      <c r="L535" s="0" t="n">
         <v>3.3</v>
       </c>
-      <c r="M535" t="n">
+      <c r="M535" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="N535" t="n">
+      <c r="N535" s="0" t="n">
         <v>3.4</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="1" t="n">
         <v>46295</v>
+      </c>
+      <c r="B536" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C536" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D536" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F536" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I536" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J536" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K536" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L536" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="M536" t="n">
+        <v>5</v>
+      </c>
+      <c r="N536" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="537">
@@ -66935,57 +67021,104 @@
       <c r="A293" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="B293" t="n">
+      <c r="B293" s="0" t="n">
         <v>4.63</v>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F293" t="n">
+      <c r="C293" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D293" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E293" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F293" s="0" t="n">
         <v>-3.65</v>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H293" t="n">
+      <c r="G293" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H293" s="0" t="n">
         <v>1.86</v>
       </c>
-      <c r="I293" t="n">
+      <c r="I293" s="0" t="n">
         <v>4.01</v>
       </c>
-      <c r="J293" t="n">
+      <c r="J293" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K293" t="n">
+      <c r="K293" s="0" t="n">
         <v>-3.85</v>
       </c>
-      <c r="L293" t="n">
+      <c r="L293" s="0" t="n">
         <v>-1.56</v>
       </c>
-      <c r="M293" t="n">
+      <c r="M293" s="0" t="n">
         <v>-4.56</v>
       </c>
-      <c r="N293" t="n">
+      <c r="N293" s="0" t="n">
         <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
         <v>46295</v>
+      </c>
+      <c r="B294" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I294" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="J294" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="L294" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M294" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="295">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25031,47 +25031,47 @@
       <c r="A536" s="1" t="n">
         <v>46295</v>
       </c>
-      <c r="B536" t="n">
+      <c r="B536" s="0" t="n">
         <v>-4.6</v>
       </c>
-      <c r="C536" t="n">
+      <c r="C536" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="D536" t="n">
+      <c r="D536" s="0" t="n">
         <v>-7.9</v>
       </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F536" t="n">
+      <c r="E536" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F536" s="0" t="n">
         <v>-9.4</v>
       </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H536" t="n">
+      <c r="G536" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H536" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="I536" t="n">
+      <c r="I536" s="0" t="n">
         <v>-2.6</v>
       </c>
-      <c r="J536" t="n">
+      <c r="J536" s="0" t="n">
         <v>-10.4</v>
       </c>
-      <c r="K536" t="n">
+      <c r="K536" s="0" t="n">
         <v>-11.6</v>
       </c>
-      <c r="L536" t="n">
+      <c r="L536" s="0" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="M536" t="n">
+      <c r="M536" s="0" t="n">
         <v>-9</v>
       </c>
-      <c r="N536" t="n">
+      <c r="N536" s="0" t="n">
         <v>-3.9</v>
       </c>
     </row>
@@ -25079,10 +25079,92 @@
       <c r="A537" s="1" t="n">
         <v>46296</v>
       </c>
+      <c r="B537" s="0" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C537" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D537" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="E537" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F537" s="0" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="G537" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H537" s="0" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="I537" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J537" s="0" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="K537" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L537" s="0" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="M537" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="N537" s="0" t="n">
+        <v>-4.9</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="1" t="n">
         <v>46297</v>
+      </c>
+      <c r="B538" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C538" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="D538" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F538" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="G538" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H538" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I538" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="J538" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="K538" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="L538" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="M538" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="N538" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="539">
@@ -50534,47 +50616,47 @@
       <c r="A536" s="1" t="n">
         <v>46295</v>
       </c>
-      <c r="B536" t="n">
+      <c r="B536" s="0" t="n">
         <v>12.1</v>
       </c>
-      <c r="C536" t="n">
+      <c r="C536" s="0" t="n">
         <v>11.8</v>
       </c>
-      <c r="D536" t="n">
+      <c r="D536" s="0" t="n">
         <v>10.7</v>
       </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F536" t="n">
+      <c r="E536" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F536" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H536" t="n">
+      <c r="G536" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H536" s="0" t="n">
         <v>10.2</v>
       </c>
-      <c r="I536" t="n">
+      <c r="I536" s="0" t="n">
         <v>12.2</v>
       </c>
-      <c r="J536" t="n">
+      <c r="J536" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K536" t="n">
+      <c r="K536" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="L536" t="n">
+      <c r="L536" s="0" t="n">
         <v>9.1</v>
       </c>
-      <c r="M536" t="n">
+      <c r="M536" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="N536" t="n">
+      <c r="N536" s="0" t="n">
         <v>6.2</v>
       </c>
     </row>
@@ -50582,10 +50664,92 @@
       <c r="A537" s="1" t="n">
         <v>46296</v>
       </c>
+      <c r="B537" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C537" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D537" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E537" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F537" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G537" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H537" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I537" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J537" s="0" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K537" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L537" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M537" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N537" s="0" t="n">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="1" t="n">
         <v>46297</v>
+      </c>
+      <c r="B538" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C538" t="n">
+        <v>12</v>
+      </c>
+      <c r="D538" t="n">
+        <v>11</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F538" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G538" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H538" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I538" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J538" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K538" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L538" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M538" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N538" t="n">
+        <v>11.7</v>
       </c>
     </row>
     <row r="539">
@@ -67073,51 +67237,51 @@
       <c r="A294" s="1" t="n">
         <v>46295</v>
       </c>
-      <c r="B294" t="n">
+      <c r="B294" s="0" t="n">
         <v>3.29</v>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F294" t="n">
+      <c r="C294" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D294" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E294" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F294" s="0" t="n">
         <v>-1.39</v>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H294" t="n">
+      <c r="G294" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H294" s="0" t="n">
         <v>4.79</v>
       </c>
-      <c r="I294" t="n">
+      <c r="I294" s="0" t="n">
         <v>3.56</v>
       </c>
-      <c r="J294" t="n">
+      <c r="J294" s="0" t="n">
         <v>-0.04</v>
       </c>
-      <c r="K294" t="n">
+      <c r="K294" s="0" t="n">
         <v>-2.31</v>
       </c>
-      <c r="L294" t="n">
+      <c r="L294" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M294" t="n">
+      <c r="M294" s="0" t="n">
         <v>-3.12</v>
       </c>
-      <c r="N294" t="n">
+      <c r="N294" s="0" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -67125,10 +67289,104 @@
       <c r="A295" s="1" t="n">
         <v>46296</v>
       </c>
+      <c r="B295" s="0" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="C295" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D295" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E295" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F295" s="0" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G295" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H295" s="0" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I295" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J295" s="0" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K295" s="0" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L295" s="0" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M295" s="0" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="N295" s="0" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
         <v>46297</v>
+      </c>
+      <c r="B296" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="I296" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="J296" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M296" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N296" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="297">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25125,51 +25125,90 @@
       <c r="A538" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="B538" t="n">
+      <c r="B538" s="0" t="n">
         <v>-1.3</v>
       </c>
-      <c r="C538" t="n">
+      <c r="C538" s="0" t="n">
         <v>-1.3</v>
       </c>
-      <c r="D538" t="n">
+      <c r="D538" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F538" t="n">
+      <c r="E538" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F538" s="0" t="n">
         <v>-3.6</v>
       </c>
-      <c r="G538" t="n">
+      <c r="G538" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="H538" t="n">
+      <c r="H538" s="0" t="n">
         <v>2.3</v>
       </c>
-      <c r="I538" t="n">
+      <c r="I538" s="0" t="n">
         <v>-1.1</v>
       </c>
-      <c r="J538" t="n">
+      <c r="J538" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="K538" t="n">
+      <c r="K538" s="0" t="n">
         <v>-6.5</v>
       </c>
-      <c r="L538" t="n">
+      <c r="L538" s="0" t="n">
         <v>-2.6</v>
       </c>
-      <c r="M538" t="n">
+      <c r="M538" s="0" t="n">
         <v>-1.2</v>
       </c>
-      <c r="N538" t="n">
+      <c r="N538" s="0" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="1" t="n">
         <v>46298</v>
+      </c>
+      <c r="B539" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C539" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="D539" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="E539" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="F539" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="G539" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="H539" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="I539" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J539" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="K539" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="L539" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="M539" t="n">
+        <v>-10</v>
+      </c>
+      <c r="N539" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="540">
@@ -50710,51 +50749,90 @@
       <c r="A538" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="B538" t="n">
+      <c r="B538" s="0" t="n">
         <v>13.1</v>
       </c>
-      <c r="C538" t="n">
+      <c r="C538" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="D538" t="n">
+      <c r="D538" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F538" t="n">
+      <c r="E538" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F538" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="G538" t="n">
+      <c r="G538" s="0" t="n">
         <v>5.6</v>
       </c>
-      <c r="H538" t="n">
+      <c r="H538" s="0" t="n">
         <v>11.1</v>
       </c>
-      <c r="I538" t="n">
+      <c r="I538" s="0" t="n">
         <v>14.3</v>
       </c>
-      <c r="J538" t="n">
+      <c r="J538" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K538" t="n">
+      <c r="K538" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="L538" t="n">
+      <c r="L538" s="0" t="n">
         <v>6.4</v>
       </c>
-      <c r="M538" t="n">
+      <c r="M538" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="N538" t="n">
+      <c r="N538" s="0" t="n">
         <v>11.7</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="1" t="n">
         <v>46298</v>
+      </c>
+      <c r="B539" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C539" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="D539" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E539" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F539" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G539" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H539" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I539" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J539" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K539" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L539" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M539" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N539" t="n">
+        <v>7.9</v>
       </c>
     </row>
     <row r="540">
@@ -67341,57 +67419,104 @@
       <c r="A296" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="B296" t="n">
+      <c r="B296" s="0" t="n">
         <v>6.69</v>
       </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F296" t="n">
+      <c r="C296" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D296" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E296" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F296" s="0" t="n">
         <v>1.24</v>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H296" t="n">
+      <c r="G296" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H296" s="0" t="n">
         <v>6.35</v>
       </c>
-      <c r="I296" t="n">
+      <c r="I296" s="0" t="n">
         <v>6.35</v>
       </c>
-      <c r="J296" t="n">
+      <c r="J296" s="0" t="n">
         <v>2.75</v>
       </c>
-      <c r="K296" t="n">
+      <c r="K296" s="0" t="n">
         <v>0.02</v>
       </c>
-      <c r="L296" t="n">
+      <c r="L296" s="0" t="n">
         <v>1.38</v>
       </c>
-      <c r="M296" t="n">
+      <c r="M296" s="0" t="n">
         <v>1.75</v>
       </c>
-      <c r="N296" t="n">
+      <c r="N296" s="0" t="n">
         <v>6.2</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
         <v>46298</v>
+      </c>
+      <c r="B297" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="I297" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J297" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K297" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="L297" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="M297" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="N297" t="n">
+        <v>2.97</v>
       </c>
     </row>
     <row r="298">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25171,49 +25171,88 @@
       <c r="A539" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="B539" t="n">
+      <c r="B539" s="0" t="n">
         <v>-2.2</v>
       </c>
-      <c r="C539" t="n">
+      <c r="C539" s="0" t="n">
         <v>-4.2</v>
       </c>
-      <c r="D539" t="n">
+      <c r="D539" s="0" t="n">
         <v>-6.7</v>
       </c>
-      <c r="E539" t="n">
+      <c r="E539" s="0" t="n">
         <v>-9.1</v>
       </c>
-      <c r="F539" t="n">
+      <c r="F539" s="0" t="n">
         <v>-9.9</v>
       </c>
-      <c r="G539" t="n">
+      <c r="G539" s="0" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H539" t="n">
+      <c r="H539" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="I539" t="n">
+      <c r="I539" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="J539" t="n">
+      <c r="J539" s="0" t="n">
         <v>-8.9</v>
       </c>
-      <c r="K539" t="n">
+      <c r="K539" s="0" t="n">
         <v>-12.5</v>
       </c>
-      <c r="L539" t="n">
+      <c r="L539" s="0" t="n">
         <v>-7.3</v>
       </c>
-      <c r="M539" t="n">
+      <c r="M539" s="0" t="n">
         <v>-10</v>
       </c>
-      <c r="N539" t="n">
+      <c r="N539" s="0" t="n">
         <v>-1.8</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="1" t="n">
         <v>46299</v>
+      </c>
+      <c r="B540" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C540" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="D540" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="E540" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="F540" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="G540" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="H540" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="I540" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="J540" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="K540" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="L540" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="M540" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="N540" t="n">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="541">
@@ -50795,49 +50834,88 @@
       <c r="A539" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="B539" t="n">
+      <c r="B539" s="0" t="n">
         <v>14.9</v>
       </c>
-      <c r="C539" t="n">
+      <c r="C539" s="0" t="n">
         <v>12.9</v>
       </c>
-      <c r="D539" t="n">
+      <c r="D539" s="0" t="n">
         <v>12.6</v>
       </c>
-      <c r="E539" t="n">
+      <c r="E539" s="0" t="n">
         <v>8.1</v>
       </c>
-      <c r="F539" t="n">
+      <c r="F539" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="G539" t="n">
+      <c r="G539" s="0" t="n">
         <v>7.7</v>
       </c>
-      <c r="H539" t="n">
+      <c r="H539" s="0" t="n">
         <v>12.2</v>
       </c>
-      <c r="I539" t="n">
+      <c r="I539" s="0" t="n">
         <v>14.2</v>
       </c>
-      <c r="J539" t="n">
+      <c r="J539" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="K539" t="n">
+      <c r="K539" s="0" t="n">
         <v>8.4</v>
       </c>
-      <c r="L539" t="n">
+      <c r="L539" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="M539" t="n">
+      <c r="M539" s="0" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="N539" t="n">
+      <c r="N539" s="0" t="n">
         <v>7.9</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="1" t="n">
         <v>46299</v>
+      </c>
+      <c r="B540" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="C540" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D540" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="E540" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F540" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G540" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H540" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I540" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J540" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K540" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L540" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M540" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N540" t="n">
+        <v>11.9</v>
       </c>
     </row>
     <row r="541">
@@ -67471,57 +67549,104 @@
       <c r="A297" s="1" t="n">
         <v>46298</v>
       </c>
-      <c r="B297" t="n">
+      <c r="B297" s="0" t="n">
         <v>5.56</v>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F297" t="n">
+      <c r="C297" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D297" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E297" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F297" s="0" t="n">
         <v>-1.24</v>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H297" t="n">
+      <c r="G297" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H297" s="0" t="n">
         <v>2.61</v>
       </c>
-      <c r="I297" t="n">
+      <c r="I297" s="0" t="n">
         <v>5.47</v>
       </c>
-      <c r="J297" t="n">
+      <c r="J297" s="0" t="n">
         <v>2.23</v>
       </c>
-      <c r="K297" t="n">
+      <c r="K297" s="0" t="n">
         <v>-1.33</v>
       </c>
-      <c r="L297" t="n">
+      <c r="L297" s="0" t="n">
         <v>-0.71</v>
       </c>
-      <c r="M297" t="n">
+      <c r="M297" s="0" t="n">
         <v>-1.66</v>
       </c>
-      <c r="N297" t="n">
+      <c r="N297" s="0" t="n">
         <v>2.97</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
         <v>46299</v>
+      </c>
+      <c r="B298" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I298" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="J298" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K298" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M298" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="N298" t="n">
+        <v>3.04</v>
       </c>
     </row>
     <row r="299">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25215,49 +25215,90 @@
       <c r="A540" s="1" t="n">
         <v>46299</v>
       </c>
-      <c r="B540" t="n">
+      <c r="B540" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="C540" t="n">
+      <c r="C540" s="0" t="n">
         <v>-2.6</v>
       </c>
-      <c r="D540" t="n">
+      <c r="D540" s="0" t="n">
         <v>-7.8</v>
       </c>
-      <c r="E540" t="n">
+      <c r="E540" s="0" t="n">
         <v>-7.8</v>
       </c>
-      <c r="F540" t="n">
+      <c r="F540" s="0" t="n">
         <v>-9.1</v>
       </c>
-      <c r="G540" t="n">
+      <c r="G540" s="0" t="n">
         <v>-10.1</v>
       </c>
-      <c r="H540" t="n">
+      <c r="H540" s="0" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="I540" t="n">
+      <c r="I540" s="0" t="n">
         <v>-1.3</v>
       </c>
-      <c r="J540" t="n">
+      <c r="J540" s="0" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="K540" t="n">
+      <c r="K540" s="0" t="n">
         <v>-12.9</v>
       </c>
-      <c r="L540" t="n">
+      <c r="L540" s="0" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="M540" t="n">
+      <c r="M540" s="0" t="n">
         <v>-9.9</v>
       </c>
-      <c r="N540" t="n">
+      <c r="N540" s="0" t="n">
         <v>-3.5</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="1" t="n">
         <v>46300</v>
+      </c>
+      <c r="B541" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C541" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D541" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F541" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="G541" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="H541" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="I541" t="n">
+        <v>3</v>
+      </c>
+      <c r="J541" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K541" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L541" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="M541" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="N541" t="n">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="542">
@@ -50878,49 +50919,90 @@
       <c r="A540" s="1" t="n">
         <v>46299</v>
       </c>
-      <c r="B540" t="n">
+      <c r="B540" s="0" t="n">
         <v>16.2</v>
       </c>
-      <c r="C540" t="n">
+      <c r="C540" s="0" t="n">
         <v>15.6</v>
       </c>
-      <c r="D540" t="n">
+      <c r="D540" s="0" t="n">
         <v>14.7</v>
       </c>
-      <c r="E540" t="n">
+      <c r="E540" s="0" t="n">
         <v>10.3</v>
       </c>
-      <c r="F540" t="n">
+      <c r="F540" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="G540" t="n">
+      <c r="G540" s="0" t="n">
         <v>10.4</v>
       </c>
-      <c r="H540" t="n">
+      <c r="H540" s="0" t="n">
         <v>16.8</v>
       </c>
-      <c r="I540" t="n">
+      <c r="I540" s="0" t="n">
         <v>14.5</v>
       </c>
-      <c r="J540" t="n">
+      <c r="J540" s="0" t="n">
         <v>13.1</v>
       </c>
-      <c r="K540" t="n">
+      <c r="K540" s="0" t="n">
         <v>8.4</v>
       </c>
-      <c r="L540" t="n">
+      <c r="L540" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="M540" t="n">
+      <c r="M540" s="0" t="n">
         <v>11.2</v>
       </c>
-      <c r="N540" t="n">
+      <c r="N540" s="0" t="n">
         <v>11.9</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="1" t="n">
         <v>46300</v>
+      </c>
+      <c r="B541" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C541" t="n">
+        <v>13</v>
+      </c>
+      <c r="D541" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F541" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G541" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H541" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I541" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J541" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K541" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L541" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M541" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N541" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="542">
@@ -67601,57 +67683,104 @@
       <c r="A298" s="1" t="n">
         <v>46299</v>
       </c>
-      <c r="B298" t="n">
+      <c r="B298" s="0" t="n">
         <v>5.67</v>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F298" t="n">
+      <c r="C298" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D298" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E298" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F298" s="0" t="n">
         <v>-0.38</v>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H298" t="n">
+      <c r="G298" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H298" s="0" t="n">
         <v>3.06</v>
       </c>
-      <c r="I298" t="n">
+      <c r="I298" s="0" t="n">
         <v>6.04</v>
       </c>
-      <c r="J298" t="n">
+      <c r="J298" s="0" t="n">
         <v>1.32</v>
       </c>
-      <c r="K298" t="n">
+      <c r="K298" s="0" t="n">
         <v>-1.79</v>
       </c>
-      <c r="L298" t="n">
+      <c r="L298" s="0" t="n">
         <v>0.11</v>
       </c>
-      <c r="M298" t="n">
+      <c r="M298" s="0" t="n">
         <v>-0.41</v>
       </c>
-      <c r="N298" t="n">
+      <c r="N298" s="0" t="n">
         <v>3.04</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
         <v>46300</v>
+      </c>
+      <c r="B299" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="I299" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="J299" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K299" t="n">
+        <v>4</v>
+      </c>
+      <c r="L299" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="M299" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N299" t="n">
+        <v>5.3</v>
       </c>
     </row>
     <row r="300">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25259,51 +25259,90 @@
       <c r="A541" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="B541" t="n">
+      <c r="B541" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="C541" t="n">
+      <c r="C541" s="0" t="n">
         <v>-0.6</v>
       </c>
-      <c r="D541" t="n">
+      <c r="D541" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F541" t="n">
+      <c r="E541" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F541" s="0" t="n">
         <v>-7.1</v>
       </c>
-      <c r="G541" t="n">
+      <c r="G541" s="0" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H541" t="n">
+      <c r="H541" s="0" t="n">
         <v>-2.6</v>
       </c>
-      <c r="I541" t="n">
+      <c r="I541" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J541" t="n">
+      <c r="J541" s="0" t="n">
         <v>-3.9</v>
       </c>
-      <c r="K541" t="n">
+      <c r="K541" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="L541" t="n">
+      <c r="L541" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="M541" t="n">
+      <c r="M541" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="N541" t="n">
+      <c r="N541" s="0" t="n">
         <v>-1.9</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="1" t="n">
         <v>46301</v>
+      </c>
+      <c r="B542" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C542" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D542" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E542" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F542" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="G542" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H542" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="I542" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J542" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K542" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L542" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M542" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N542" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="543">
@@ -50963,51 +51002,90 @@
       <c r="A541" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="B541" t="n">
+      <c r="B541" s="0" t="n">
         <v>13.8</v>
       </c>
-      <c r="C541" t="n">
+      <c r="C541" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="D541" t="n">
+      <c r="D541" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F541" t="n">
+      <c r="E541" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F541" s="0" t="n">
         <v>15.6</v>
       </c>
-      <c r="G541" t="n">
+      <c r="G541" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="H541" t="n">
+      <c r="H541" s="0" t="n">
         <v>18.7</v>
       </c>
-      <c r="I541" t="n">
+      <c r="I541" s="0" t="n">
         <v>13.1</v>
       </c>
-      <c r="J541" t="n">
+      <c r="J541" s="0" t="n">
         <v>15.5</v>
       </c>
-      <c r="K541" t="n">
+      <c r="K541" s="0" t="n">
         <v>14.4</v>
       </c>
-      <c r="L541" t="n">
+      <c r="L541" s="0" t="n">
         <v>15.6</v>
       </c>
-      <c r="M541" t="n">
+      <c r="M541" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="N541" t="n">
+      <c r="N541" s="0" t="n">
         <v>14.7</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="1" t="n">
         <v>46301</v>
+      </c>
+      <c r="B542" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="C542" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D542" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E542" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F542" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G542" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H542" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I542" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J542" t="n">
+        <v>14</v>
+      </c>
+      <c r="K542" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L542" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="M542" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N542" t="n">
+        <v>16.4</v>
       </c>
     </row>
     <row r="543">
@@ -67735,57 +67813,104 @@
       <c r="A299" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="B299" t="n">
+      <c r="B299" s="0" t="n">
         <v>6.8</v>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F299" t="n">
+      <c r="C299" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D299" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E299" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F299" s="0" t="n">
         <v>1.79</v>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H299" t="n">
+      <c r="G299" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H299" s="0" t="n">
         <v>6.15</v>
       </c>
-      <c r="I299" t="n">
+      <c r="I299" s="0" t="n">
         <v>7.22</v>
       </c>
-      <c r="J299" t="n">
+      <c r="J299" s="0" t="n">
         <v>4.58</v>
       </c>
-      <c r="K299" t="n">
+      <c r="K299" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="L299" t="n">
+      <c r="L299" s="0" t="n">
         <v>3.31</v>
       </c>
-      <c r="M299" t="n">
+      <c r="M299" s="0" t="n">
         <v>3.04</v>
       </c>
-      <c r="N299" t="n">
+      <c r="N299" s="0" t="n">
         <v>5.3</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
         <v>46301</v>
+      </c>
+      <c r="B300" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I300" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="J300" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K300" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="L300" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="M300" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="N300" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="301">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25305,49 +25305,88 @@
       <c r="A542" s="1" t="n">
         <v>46301</v>
       </c>
-      <c r="B542" t="n">
+      <c r="B542" s="0" t="n">
         <v>5.5</v>
       </c>
-      <c r="C542" t="n">
+      <c r="C542" s="0" t="n">
         <v>5.5</v>
       </c>
-      <c r="D542" t="n">
+      <c r="D542" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="E542" t="n">
+      <c r="E542" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F542" t="n">
+      <c r="F542" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="G542" t="n">
+      <c r="G542" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="H542" t="n">
+      <c r="H542" s="0" t="n">
         <v>-3.3</v>
       </c>
-      <c r="I542" t="n">
+      <c r="I542" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J542" t="n">
+      <c r="J542" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="K542" t="n">
+      <c r="K542" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="L542" t="n">
+      <c r="L542" s="0" t="n">
         <v>3.7</v>
       </c>
-      <c r="M542" t="n">
+      <c r="M542" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="N542" t="n">
+      <c r="N542" s="0" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="1" t="n">
         <v>46302</v>
+      </c>
+      <c r="B543" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C543" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D543" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="E543" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F543" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="G543" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H543" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J543" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="K543" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="L543" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="M543" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="N543" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="544">
@@ -51048,49 +51087,88 @@
       <c r="A542" s="1" t="n">
         <v>46301</v>
       </c>
-      <c r="B542" t="n">
+      <c r="B542" s="0" t="n">
         <v>13.9</v>
       </c>
-      <c r="C542" t="n">
+      <c r="C542" s="0" t="n">
         <v>11.8</v>
       </c>
-      <c r="D542" t="n">
+      <c r="D542" s="0" t="n">
         <v>14.8</v>
       </c>
-      <c r="E542" t="n">
+      <c r="E542" s="0" t="n">
         <v>14.8</v>
       </c>
-      <c r="F542" t="n">
+      <c r="F542" s="0" t="n">
         <v>15.2</v>
       </c>
-      <c r="G542" t="n">
+      <c r="G542" s="0" t="n">
         <v>9.1</v>
       </c>
-      <c r="H542" t="n">
+      <c r="H542" s="0" t="n">
         <v>14.1</v>
       </c>
-      <c r="I542" t="n">
+      <c r="I542" s="0" t="n">
         <v>15.2</v>
       </c>
-      <c r="J542" t="n">
+      <c r="J542" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="K542" t="n">
+      <c r="K542" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="L542" t="n">
+      <c r="L542" s="0" t="n">
         <v>15.7</v>
       </c>
-      <c r="M542" t="n">
+      <c r="M542" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="N542" t="n">
+      <c r="N542" s="0" t="n">
         <v>16.4</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="1" t="n">
         <v>46302</v>
+      </c>
+      <c r="B543" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C543" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D543" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E543" t="n">
+        <v>13</v>
+      </c>
+      <c r="F543" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G543" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H543" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I543" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J543" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K543" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L543" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="M543" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N543" t="n">
+        <v>16.2</v>
       </c>
     </row>
     <row r="544">
@@ -67865,57 +67943,104 @@
       <c r="A300" s="1" t="n">
         <v>46301</v>
       </c>
-      <c r="B300" t="n">
+      <c r="B300" s="0" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F300" t="n">
+      <c r="C300" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D300" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E300" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F300" s="0" t="n">
         <v>4.68</v>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H300" t="n">
+      <c r="G300" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H300" s="0" t="n">
         <v>4.98</v>
       </c>
-      <c r="I300" t="n">
+      <c r="I300" s="0" t="n">
         <v>8.68</v>
       </c>
-      <c r="J300" t="n">
+      <c r="J300" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="K300" t="n">
+      <c r="K300" s="0" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="L300" t="n">
+      <c r="L300" s="0" t="n">
         <v>8.41</v>
       </c>
-      <c r="M300" t="n">
+      <c r="M300" s="0" t="n">
         <v>5.53</v>
       </c>
-      <c r="N300" t="n">
+      <c r="N300" s="0" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
         <v>46302</v>
+      </c>
+      <c r="B301" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="I301" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="J301" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="K301" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="L301" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="M301" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="N301" t="n">
+        <v>10.34</v>
       </c>
     </row>
     <row r="302">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25349,49 +25349,90 @@
       <c r="A543" s="1" t="n">
         <v>46302</v>
       </c>
-      <c r="B543" t="n">
+      <c r="B543" s="0" t="n">
         <v>0.9</v>
       </c>
-      <c r="C543" t="n">
+      <c r="C543" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="D543" t="n">
+      <c r="D543" s="0" t="n">
         <v>-2.7</v>
       </c>
-      <c r="E543" t="n">
+      <c r="E543" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F543" t="n">
+      <c r="F543" s="0" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G543" t="n">
+      <c r="G543" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H543" t="n">
+      <c r="H543" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="I543" t="n">
+      <c r="I543" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="J543" t="n">
+      <c r="J543" s="0" t="n">
         <v>-5.2</v>
       </c>
-      <c r="K543" t="n">
+      <c r="K543" s="0" t="n">
         <v>-1.8</v>
       </c>
-      <c r="L543" t="n">
+      <c r="L543" s="0" t="n">
         <v>-1.4</v>
       </c>
-      <c r="M543" t="n">
+      <c r="M543" s="0" t="n">
         <v>-1.8</v>
       </c>
-      <c r="N543" t="n">
+      <c r="N543" s="0" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="1" t="n">
         <v>46303</v>
+      </c>
+      <c r="B544" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="C544" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="D544" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F544" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="G544" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H544" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="K544" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L544" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M544" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N544" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="545">
@@ -51131,49 +51172,90 @@
       <c r="A543" s="1" t="n">
         <v>46302</v>
       </c>
-      <c r="B543" t="n">
+      <c r="B543" s="0" t="n">
         <v>15.4</v>
       </c>
-      <c r="C543" t="n">
+      <c r="C543" s="0" t="n">
         <v>13.7</v>
       </c>
-      <c r="D543" t="n">
+      <c r="D543" s="0" t="n">
         <v>12.4</v>
       </c>
-      <c r="E543" t="n">
+      <c r="E543" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="F543" t="n">
+      <c r="F543" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="G543" t="n">
+      <c r="G543" s="0" t="n">
         <v>9.5</v>
       </c>
-      <c r="H543" t="n">
+      <c r="H543" s="0" t="n">
         <v>15.7</v>
       </c>
-      <c r="I543" t="n">
+      <c r="I543" s="0" t="n">
         <v>15.6</v>
       </c>
-      <c r="J543" t="n">
+      <c r="J543" s="0" t="n">
         <v>12.2</v>
       </c>
-      <c r="K543" t="n">
+      <c r="K543" s="0" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="L543" t="n">
+      <c r="L543" s="0" t="n">
         <v>14.1</v>
       </c>
-      <c r="M543" t="n">
+      <c r="M543" s="0" t="n">
         <v>11.1</v>
       </c>
-      <c r="N543" t="n">
+      <c r="N543" s="0" t="n">
         <v>16.2</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="1" t="n">
         <v>46303</v>
+      </c>
+      <c r="B544" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C544" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D544" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F544" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G544" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H544" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I544" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J544" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K544" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L544" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M544" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N544" t="n">
+        <v>16.5</v>
       </c>
     </row>
     <row r="545">
@@ -67995,57 +68077,104 @@
       <c r="A301" s="1" t="n">
         <v>46302</v>
       </c>
-      <c r="B301" t="n">
+      <c r="B301" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F301" t="n">
+      <c r="C301" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D301" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E301" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F301" s="0" t="n">
         <v>4.49</v>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H301" t="n">
+      <c r="G301" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H301" s="0" t="n">
         <v>8.34</v>
       </c>
-      <c r="I301" t="n">
+      <c r="I301" s="0" t="n">
         <v>6.91</v>
       </c>
-      <c r="J301" t="n">
+      <c r="J301" s="0" t="n">
         <v>3.94</v>
       </c>
-      <c r="K301" t="n">
+      <c r="K301" s="0" t="n">
         <v>5.33</v>
       </c>
-      <c r="L301" t="n">
+      <c r="L301" s="0" t="n">
         <v>6.03</v>
       </c>
-      <c r="M301" t="n">
+      <c r="M301" s="0" t="n">
         <v>4.41</v>
       </c>
-      <c r="N301" t="n">
+      <c r="N301" s="0" t="n">
         <v>10.34</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
         <v>46303</v>
+      </c>
+      <c r="B302" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="I302" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="J302" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="K302" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L302" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N302" t="n">
+        <v>10.3</v>
       </c>
     </row>
     <row r="303">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25393,51 +25393,90 @@
       <c r="A544" s="1" t="n">
         <v>46303</v>
       </c>
-      <c r="B544" t="n">
+      <c r="B544" s="0" t="n">
         <v>-2.4</v>
       </c>
-      <c r="C544" t="n">
+      <c r="C544" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="D544" t="n">
+      <c r="D544" s="0" t="n">
         <v>-3.2</v>
       </c>
-      <c r="E544" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F544" t="n">
+      <c r="E544" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F544" s="0" t="n">
         <v>-6.2</v>
       </c>
-      <c r="G544" t="n">
+      <c r="G544" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="H544" t="n">
+      <c r="H544" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I544" t="n">
+      <c r="I544" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="J544" t="n">
+      <c r="J544" s="0" t="n">
         <v>-3.7</v>
       </c>
-      <c r="K544" t="n">
+      <c r="K544" s="0" t="n">
         <v>-5.5</v>
       </c>
-      <c r="L544" t="n">
+      <c r="L544" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="M544" t="n">
+      <c r="M544" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="N544" t="n">
+      <c r="N544" s="0" t="n">
         <v>6.6</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="1" t="n">
         <v>46304</v>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C545" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D545" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E545" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="F545" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="G545" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="H545" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="I545" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="K545" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="L545" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="M545" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="N545" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="546">
@@ -51216,51 +51255,90 @@
       <c r="A544" s="1" t="n">
         <v>46303</v>
       </c>
-      <c r="B544" t="n">
+      <c r="B544" s="0" t="n">
         <v>13.8</v>
       </c>
-      <c r="C544" t="n">
+      <c r="C544" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="D544" t="n">
+      <c r="D544" s="0" t="n">
         <v>10.9</v>
       </c>
-      <c r="E544" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F544" t="n">
+      <c r="E544" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F544" s="0" t="n">
         <v>7.1</v>
       </c>
-      <c r="G544" t="n">
+      <c r="G544" s="0" t="n">
         <v>6.7</v>
       </c>
-      <c r="H544" t="n">
+      <c r="H544" s="0" t="n">
         <v>15.4</v>
       </c>
-      <c r="I544" t="n">
+      <c r="I544" s="0" t="n">
         <v>12.6</v>
       </c>
-      <c r="J544" t="n">
+      <c r="J544" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="K544" t="n">
+      <c r="K544" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="L544" t="n">
+      <c r="L544" s="0" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M544" t="n">
+      <c r="M544" s="0" t="n">
         <v>6.4</v>
       </c>
-      <c r="N544" t="n">
+      <c r="N544" s="0" t="n">
         <v>16.5</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="1" t="n">
         <v>46304</v>
+      </c>
+      <c r="B545" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C545" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D545" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E545" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F545" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G545" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H545" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I545" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J545" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="K545" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L545" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M545" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="N545" t="n">
+        <v>14.4</v>
       </c>
     </row>
     <row r="546">
@@ -68129,57 +68207,104 @@
       <c r="A302" s="1" t="n">
         <v>46303</v>
       </c>
-      <c r="B302" t="n">
+      <c r="B302" s="0" t="n">
         <v>6.4</v>
       </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F302" t="n">
+      <c r="C302" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D302" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E302" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F302" s="0" t="n">
         <v>0.98</v>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H302" t="n">
+      <c r="G302" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H302" s="0" t="n">
         <v>6.91</v>
       </c>
-      <c r="I302" t="n">
+      <c r="I302" s="0" t="n">
         <v>7.81</v>
       </c>
-      <c r="J302" t="n">
+      <c r="J302" s="0" t="n">
         <v>4.54</v>
       </c>
-      <c r="K302" t="n">
+      <c r="K302" s="0" t="n">
         <v>1.6</v>
       </c>
-      <c r="L302" t="n">
+      <c r="L302" s="0" t="n">
         <v>3.21</v>
       </c>
-      <c r="M302" t="n">
+      <c r="M302" s="0" t="n">
         <v>0.73</v>
       </c>
-      <c r="N302" t="n">
+      <c r="N302" s="0" t="n">
         <v>10.3</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
         <v>46304</v>
+      </c>
+      <c r="B303" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="I303" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="J303" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K303" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M303" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="N303" t="n">
+        <v>6.41</v>
       </c>
     </row>
     <row r="304">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25439,49 +25439,90 @@
       <c r="A545" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="B545" t="n">
+      <c r="B545" s="0" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C545" t="n">
+      <c r="C545" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="D545" t="n">
+      <c r="D545" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="E545" t="n">
+      <c r="E545" s="0" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="F545" t="n">
+      <c r="F545" s="0" t="n">
         <v>-11.2</v>
       </c>
-      <c r="G545" t="n">
+      <c r="G545" s="0" t="n">
         <v>-10.3</v>
       </c>
-      <c r="H545" t="n">
+      <c r="H545" s="0" t="n">
         <v>-2.5</v>
       </c>
-      <c r="I545" t="n">
+      <c r="I545" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="J545" t="n">
+      <c r="J545" s="0" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="K545" t="n">
+      <c r="K545" s="0" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="L545" t="n">
+      <c r="L545" s="0" t="n">
         <v>-7.7</v>
       </c>
-      <c r="M545" t="n">
+      <c r="M545" s="0" t="n">
         <v>-11.2</v>
       </c>
-      <c r="N545" t="n">
+      <c r="N545" s="0" t="n">
         <v>-0.9</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="1" t="n">
         <v>46305</v>
+      </c>
+      <c r="B546" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C546" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D546" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F546" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="G546" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="H546" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="I546" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J546" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K546" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L546" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M546" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N546" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="547">
@@ -51301,49 +51342,90 @@
       <c r="A545" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="B545" t="n">
+      <c r="B545" s="0" t="n">
         <v>14.7</v>
       </c>
-      <c r="C545" t="n">
+      <c r="C545" s="0" t="n">
         <v>17.4</v>
       </c>
-      <c r="D545" t="n">
+      <c r="D545" s="0" t="n">
         <v>15.4</v>
       </c>
-      <c r="E545" t="n">
+      <c r="E545" s="0" t="n">
         <v>11.1</v>
       </c>
-      <c r="F545" t="n">
+      <c r="F545" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="G545" t="n">
+      <c r="G545" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="H545" t="n">
+      <c r="H545" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="I545" t="n">
+      <c r="I545" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="J545" t="n">
+      <c r="J545" s="0" t="n">
         <v>12.9</v>
       </c>
-      <c r="K545" t="n">
+      <c r="K545" s="0" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L545" t="n">
+      <c r="L545" s="0" t="n">
         <v>11.7</v>
       </c>
-      <c r="M545" t="n">
+      <c r="M545" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="N545" t="n">
+      <c r="N545" s="0" t="n">
         <v>14.4</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="1" t="n">
         <v>46305</v>
+      </c>
+      <c r="B546" t="n">
+        <v>13</v>
+      </c>
+      <c r="C546" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="D546" t="n">
+        <v>12</v>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F546" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G546" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H546" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="I546" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J546" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K546" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L546" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M546" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N546" t="n">
+        <v>16.3</v>
       </c>
     </row>
     <row r="547">
@@ -68259,57 +68341,104 @@
       <c r="A303" s="1" t="n">
         <v>46304</v>
       </c>
-      <c r="B303" t="n">
+      <c r="B303" s="0" t="n">
         <v>5.88</v>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F303" t="n">
+      <c r="C303" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D303" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E303" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F303" s="0" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H303" t="n">
+      <c r="G303" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H303" s="0" t="n">
         <v>3.01</v>
       </c>
-      <c r="I303" t="n">
+      <c r="I303" s="0" t="n">
         <v>5.13</v>
       </c>
-      <c r="J303" t="n">
+      <c r="J303" s="0" t="n">
         <v>1.75</v>
       </c>
-      <c r="K303" t="n">
+      <c r="K303" s="0" t="n">
         <v>1.04</v>
       </c>
-      <c r="L303" t="n">
+      <c r="L303" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="M303" t="n">
+      <c r="M303" s="0" t="n">
         <v>-2.16</v>
       </c>
-      <c r="N303" t="n">
+      <c r="N303" s="0" t="n">
         <v>6.41</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
         <v>46305</v>
+      </c>
+      <c r="B304" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="I304" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J304" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="K304" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L304" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M304" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="N304" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="305">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25483,45 +25483,45 @@
       <c r="A546" s="1" t="n">
         <v>46305</v>
       </c>
-      <c r="B546" t="n">
+      <c r="B546" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="C546" t="n">
+      <c r="C546" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="D546" t="n">
+      <c r="D546" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F546" t="n">
+      <c r="E546" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F546" s="0" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G546" t="n">
+      <c r="G546" s="0" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H546" t="n">
+      <c r="H546" s="0" t="n">
         <v>-4.5</v>
       </c>
-      <c r="I546" t="n">
+      <c r="I546" s="0" t="n">
         <v>3.1</v>
       </c>
-      <c r="J546" t="n">
+      <c r="J546" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="K546" t="n">
+      <c r="K546" s="0" t="n">
         <v>-0.4</v>
       </c>
-      <c r="L546" t="n">
+      <c r="L546" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="M546" t="n">
+      <c r="M546" s="0" t="n">
         <v>-2.9</v>
       </c>
-      <c r="N546" t="n">
+      <c r="N546" s="0" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -25529,10 +25529,90 @@
       <c r="A547" s="1" t="n">
         <v>46306</v>
       </c>
+      <c r="B547" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="C547" s="0" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="D547" s="0" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E547" s="0" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="F547" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G547" s="0" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="H547" s="0" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="I547" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J547" s="0" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="K547" s="0" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L547" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="M547" s="0" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="N547" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="1" t="n">
         <v>46307</v>
+      </c>
+      <c r="B548" t="n">
+        <v>-5</v>
+      </c>
+      <c r="C548" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="D548" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F548" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="G548" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="H548" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I548" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="J548" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="K548" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="L548" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="M548" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="N548" t="n">
+        <v>-4.4</v>
       </c>
     </row>
     <row r="549">
@@ -51386,45 +51466,45 @@
       <c r="A546" s="1" t="n">
         <v>46305</v>
       </c>
-      <c r="B546" t="n">
+      <c r="B546" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="C546" t="n">
+      <c r="C546" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="D546" t="n">
+      <c r="D546" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F546" t="n">
+      <c r="E546" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F546" s="0" t="n">
         <v>7.7</v>
       </c>
-      <c r="G546" t="n">
+      <c r="G546" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="H546" t="n">
+      <c r="H546" s="0" t="n">
         <v>19.7</v>
       </c>
-      <c r="I546" t="n">
+      <c r="I546" s="0" t="n">
         <v>13.7</v>
       </c>
-      <c r="J546" t="n">
+      <c r="J546" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="K546" t="n">
+      <c r="K546" s="0" t="n">
         <v>6.5</v>
       </c>
-      <c r="L546" t="n">
+      <c r="L546" s="0" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M546" t="n">
+      <c r="M546" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="N546" t="n">
+      <c r="N546" s="0" t="n">
         <v>16.3</v>
       </c>
     </row>
@@ -51432,10 +51512,90 @@
       <c r="A547" s="1" t="n">
         <v>46306</v>
       </c>
+      <c r="B547" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C547" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D547" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E547" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F547" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G547" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H547" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I547" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J547" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K547" s="0" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L547" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M547" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N547" s="0" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="1" t="n">
         <v>46307</v>
+      </c>
+      <c r="B548" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="C548" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D548" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F548" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G548" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H548" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I548" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J548" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K548" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L548" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M548" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N548" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="549">
@@ -68393,51 +68553,51 @@
       <c r="A304" s="1" t="n">
         <v>46305</v>
       </c>
-      <c r="B304" t="n">
+      <c r="B304" s="0" t="n">
         <v>6.34</v>
       </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F304" t="n">
+      <c r="C304" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D304" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E304" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F304" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H304" t="n">
+      <c r="G304" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H304" s="0" t="n">
         <v>5.79</v>
       </c>
-      <c r="I304" t="n">
+      <c r="I304" s="0" t="n">
         <v>7.3</v>
       </c>
-      <c r="J304" t="n">
+      <c r="J304" s="0" t="n">
         <v>6.28</v>
       </c>
-      <c r="K304" t="n">
+      <c r="K304" s="0" t="n">
         <v>3.71</v>
       </c>
-      <c r="L304" t="n">
+      <c r="L304" s="0" t="n">
         <v>2.68</v>
       </c>
-      <c r="M304" t="n">
+      <c r="M304" s="0" t="n">
         <v>1.84</v>
       </c>
-      <c r="N304" t="n">
+      <c r="N304" s="0" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -68445,10 +68605,104 @@
       <c r="A305" s="1" t="n">
         <v>46306</v>
       </c>
+      <c r="B305" s="0" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="C305" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D305" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E305" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F305" s="0" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="G305" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H305" s="0" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I305" s="0" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J305" s="0" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K305" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L305" s="0" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="M305" s="0" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="N305" s="0" t="n">
+        <v>5.38</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
         <v>46307</v>
+      </c>
+      <c r="B306" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I306" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J306" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="K306" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="L306" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="M306" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="307">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25573,45 +25573,45 @@
       <c r="A548" s="1" t="n">
         <v>46307</v>
       </c>
-      <c r="B548" t="n">
+      <c r="B548" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="C548" t="n">
+      <c r="C548" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="D548" t="n">
+      <c r="D548" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="E548" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F548" t="n">
+      <c r="E548" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F548" s="0" t="n">
         <v>-10.7</v>
       </c>
-      <c r="G548" t="n">
+      <c r="G548" s="0" t="n">
         <v>-8.4</v>
       </c>
-      <c r="H548" t="n">
+      <c r="H548" s="0" t="n">
         <v>-3.7</v>
       </c>
-      <c r="I548" t="n">
+      <c r="I548" s="0" t="n">
         <v>-5.3</v>
       </c>
-      <c r="J548" t="n">
+      <c r="J548" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="K548" t="n">
+      <c r="K548" s="0" t="n">
         <v>-14.2</v>
       </c>
-      <c r="L548" t="n">
+      <c r="L548" s="0" t="n">
         <v>-7.4</v>
       </c>
-      <c r="M548" t="n">
+      <c r="M548" s="0" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="N548" t="n">
+      <c r="N548" s="0" t="n">
         <v>-4.4</v>
       </c>
     </row>
@@ -25619,10 +25619,90 @@
       <c r="A549" s="1" t="n">
         <v>46308</v>
       </c>
+      <c r="B549" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="C549" s="0" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="D549" s="0" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="E549" s="0" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="F549" s="0" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="G549" s="0" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="H549" s="0" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="I549" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="J549" s="0" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="K549" s="0" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="L549" s="0" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="M549" s="0" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="N549" s="0" t="n">
+        <v>-5.4</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="1" t="n">
         <v>46309</v>
+      </c>
+      <c r="B550" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C550" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D550" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F550" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="G550" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H550" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="I550" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J550" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="K550" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L550" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="M550" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N550" t="n">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="551">
@@ -51556,45 +51636,45 @@
       <c r="A548" s="1" t="n">
         <v>46307</v>
       </c>
-      <c r="B548" t="n">
+      <c r="B548" s="0" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="C548" t="n">
+      <c r="C548" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="D548" t="n">
+      <c r="D548" s="0" t="n">
         <v>6.8</v>
       </c>
-      <c r="E548" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F548" t="n">
+      <c r="E548" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F548" s="0" t="n">
         <v>3.8</v>
       </c>
-      <c r="G548" t="n">
+      <c r="G548" s="0" t="n">
         <v>2.9</v>
       </c>
-      <c r="H548" t="n">
+      <c r="H548" s="0" t="n">
         <v>7.5</v>
       </c>
-      <c r="I548" t="n">
+      <c r="I548" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J548" t="n">
+      <c r="J548" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="K548" t="n">
+      <c r="K548" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="L548" t="n">
+      <c r="L548" s="0" t="n">
         <v>4.8</v>
       </c>
-      <c r="M548" t="n">
+      <c r="M548" s="0" t="n">
         <v>4.3</v>
       </c>
-      <c r="N548" t="n">
+      <c r="N548" s="0" t="n">
         <v>6.8</v>
       </c>
     </row>
@@ -51602,10 +51682,90 @@
       <c r="A549" s="1" t="n">
         <v>46308</v>
       </c>
+      <c r="B549" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C549" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D549" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E549" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F549" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G549" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H549" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I549" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J549" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K549" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L549" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M549" s="0" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N549" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="1" t="n">
         <v>46309</v>
+      </c>
+      <c r="B550" t="n">
+        <v>9</v>
+      </c>
+      <c r="C550" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D550" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F550" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G550" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H550" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I550" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J550" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K550" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L550" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M550" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N550" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="551">
@@ -68657,51 +68817,51 @@
       <c r="A306" s="1" t="n">
         <v>46307</v>
       </c>
-      <c r="B306" t="n">
+      <c r="B306" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F306" t="n">
+      <c r="C306" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D306" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E306" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F306" s="0" t="n">
         <v>-4.04</v>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H306" t="n">
+      <c r="G306" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H306" s="0" t="n">
         <v>1.81</v>
       </c>
-      <c r="I306" t="n">
+      <c r="I306" s="0" t="n">
         <v>1.38</v>
       </c>
-      <c r="J306" t="n">
+      <c r="J306" s="0" t="n">
         <v>-0.43</v>
       </c>
-      <c r="K306" t="n">
+      <c r="K306" s="0" t="n">
         <v>-6.96</v>
       </c>
-      <c r="L306" t="n">
+      <c r="L306" s="0" t="n">
         <v>-1.56</v>
       </c>
-      <c r="M306" t="n">
+      <c r="M306" s="0" t="n">
         <v>-3.68</v>
       </c>
-      <c r="N306" t="n">
+      <c r="N306" s="0" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -68709,10 +68869,104 @@
       <c r="A307" s="1" t="n">
         <v>46308</v>
       </c>
+      <c r="B307" s="0" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C307" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D307" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E307" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F307" s="0" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="G307" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H307" s="0" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I307" s="0" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J307" s="0" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="K307" s="0" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="L307" s="0" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="M307" s="0" t="n">
+        <v>-5.23</v>
+      </c>
+      <c r="N307" s="0" t="n">
+        <v>0.76</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
         <v>46309</v>
+      </c>
+      <c r="B308" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I308" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K308" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M308" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="N308" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="309">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25663,51 +25663,90 @@
       <c r="A550" s="1" t="n">
         <v>46309</v>
       </c>
-      <c r="B550" t="n">
+      <c r="B550" s="0" t="n">
         <v>-1.8</v>
       </c>
-      <c r="C550" t="n">
+      <c r="C550" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="D550" t="n">
+      <c r="D550" s="0" t="n">
         <v>-2.3</v>
       </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F550" t="n">
+      <c r="E550" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F550" s="0" t="n">
         <v>-5.5</v>
       </c>
-      <c r="G550" t="n">
+      <c r="G550" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="H550" t="n">
+      <c r="H550" s="0" t="n">
         <v>-3.7</v>
       </c>
-      <c r="I550" t="n">
+      <c r="I550" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="J550" t="n">
+      <c r="J550" s="0" t="n">
         <v>-1.7</v>
       </c>
-      <c r="K550" t="n">
+      <c r="K550" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="L550" t="n">
+      <c r="L550" s="0" t="n">
         <v>-0.9</v>
       </c>
-      <c r="M550" t="n">
+      <c r="M550" s="0" t="n">
         <v>-7</v>
       </c>
-      <c r="N550" t="n">
+      <c r="N550" s="0" t="n">
         <v>-2.9</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="1" t="n">
         <v>46310</v>
+      </c>
+      <c r="B551" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C551" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D551" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="E551" t="n">
+        <v>-9</v>
+      </c>
+      <c r="F551" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="G551" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="H551" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="I551" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="J551" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="K551" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="L551" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M551" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N551" t="n">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="552">
@@ -51726,51 +51765,90 @@
       <c r="A550" s="1" t="n">
         <v>46309</v>
       </c>
-      <c r="B550" t="n">
+      <c r="B550" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="C550" t="n">
+      <c r="C550" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="D550" t="n">
+      <c r="D550" s="0" t="n">
         <v>6.1</v>
       </c>
-      <c r="E550" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F550" t="n">
+      <c r="E550" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F550" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="G550" t="n">
+      <c r="G550" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="H550" t="n">
+      <c r="H550" s="0" t="n">
         <v>10.2</v>
       </c>
-      <c r="I550" t="n">
+      <c r="I550" s="0" t="n">
         <v>8.6</v>
       </c>
-      <c r="J550" t="n">
+      <c r="J550" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="K550" t="n">
+      <c r="K550" s="0" t="n">
         <v>3.3</v>
       </c>
-      <c r="L550" t="n">
+      <c r="L550" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="M550" t="n">
+      <c r="M550" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="N550" t="n">
+      <c r="N550" s="0" t="n">
         <v>7.4</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="1" t="n">
         <v>46310</v>
+      </c>
+      <c r="B551" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C551" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D551" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E551" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G551" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H551" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>5</v>
+      </c>
+      <c r="J551" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K551" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L551" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M551" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="N551" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="552">
@@ -68921,57 +68999,104 @@
       <c r="A308" s="1" t="n">
         <v>46309</v>
       </c>
-      <c r="B308" t="n">
+      <c r="B308" s="0" t="n">
         <v>3.04</v>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F308" t="n">
+      <c r="C308" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D308" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E308" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F308" s="0" t="n">
         <v>-0.75</v>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H308" t="n">
+      <c r="G308" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H308" s="0" t="n">
         <v>1.94</v>
       </c>
-      <c r="I308" t="n">
+      <c r="I308" s="0" t="n">
         <v>3.63</v>
       </c>
-      <c r="J308" t="n">
+      <c r="J308" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="K308" t="n">
+      <c r="K308" s="0" t="n">
         <v>-2.49</v>
       </c>
-      <c r="L308" t="n">
+      <c r="L308" s="0" t="n">
         <v>0.99</v>
       </c>
-      <c r="M308" t="n">
+      <c r="M308" s="0" t="n">
         <v>-2.24</v>
       </c>
-      <c r="N308" t="n">
+      <c r="N308" s="0" t="n">
         <v>2.04</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
         <v>46310</v>
+      </c>
+      <c r="B309" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I309" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J309" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="K309" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="L309" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="M309" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="N309" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="310">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25709,49 +25709,90 @@
       <c r="A551" s="1" t="n">
         <v>46310</v>
       </c>
-      <c r="B551" t="n">
+      <c r="B551" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="C551" t="n">
+      <c r="C551" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="D551" t="n">
+      <c r="D551" s="0" t="n">
         <v>-4.4</v>
       </c>
-      <c r="E551" t="n">
+      <c r="E551" s="0" t="n">
         <v>-9</v>
       </c>
-      <c r="F551" t="n">
+      <c r="F551" s="0" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="G551" t="n">
+      <c r="G551" s="0" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H551" t="n">
+      <c r="H551" s="0" t="n">
         <v>-2.4</v>
       </c>
-      <c r="I551" t="n">
+      <c r="I551" s="0" t="n">
         <v>-0.8</v>
       </c>
-      <c r="J551" t="n">
+      <c r="J551" s="0" t="n">
         <v>-10.2</v>
       </c>
-      <c r="K551" t="n">
+      <c r="K551" s="0" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="L551" t="n">
+      <c r="L551" s="0" t="n">
         <v>-9</v>
       </c>
-      <c r="M551" t="n">
+      <c r="M551" s="0" t="n">
         <v>-11</v>
       </c>
-      <c r="N551" t="n">
+      <c r="N551" s="0" t="n">
         <v>-3.5</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="1" t="n">
         <v>46311</v>
+      </c>
+      <c r="B552" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="C552" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="D552" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F552" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="G552" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="H552" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="I552" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="J552" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K552" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="L552" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="M552" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="N552" t="n">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="553">
@@ -51811,49 +51852,90 @@
       <c r="A551" s="1" t="n">
         <v>46310</v>
       </c>
-      <c r="B551" t="n">
+      <c r="B551" s="0" t="n">
         <v>4.8</v>
       </c>
-      <c r="C551" t="n">
+      <c r="C551" s="0" t="n">
         <v>3.4</v>
       </c>
-      <c r="D551" t="n">
+      <c r="D551" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="E551" t="n">
+      <c r="E551" s="0" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F551" t="n">
+      <c r="F551" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="G551" t="n">
+      <c r="G551" s="0" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H551" t="n">
+      <c r="H551" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="I551" t="n">
+      <c r="I551" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J551" t="n">
+      <c r="J551" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="K551" t="n">
+      <c r="K551" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="L551" t="n">
+      <c r="L551" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="M551" t="n">
+      <c r="M551" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="N551" t="n">
+      <c r="N551" s="0" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="1" t="n">
         <v>46311</v>
+      </c>
+      <c r="B552" t="n">
+        <v>3</v>
+      </c>
+      <c r="C552" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D552" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F552" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="G552" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H552" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I552" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J552" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="K552" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L552" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="M552" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="N552" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="553">
@@ -69051,57 +69133,106 @@
       <c r="A309" s="1" t="n">
         <v>46310</v>
       </c>
-      <c r="B309" t="n">
+      <c r="B309" s="0" t="n">
         <v>2.21</v>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F309" t="n">
+      <c r="C309" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D309" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E309" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F309" s="0" t="n">
         <v>-4.39</v>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H309" t="n">
+      <c r="G309" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H309" s="0" t="n">
         <v>1.84</v>
       </c>
-      <c r="I309" t="n">
+      <c r="I309" s="0" t="n">
         <v>1.06</v>
       </c>
-      <c r="J309" t="n">
+      <c r="J309" s="0" t="n">
         <v>-4.63</v>
       </c>
-      <c r="K309" t="n">
+      <c r="K309" s="0" t="n">
         <v>-4.38</v>
       </c>
-      <c r="L309" t="n">
+      <c r="L309" s="0" t="n">
         <v>-4.29</v>
       </c>
-      <c r="M309" t="n">
+      <c r="M309" s="0" t="n">
         <v>-5.19</v>
       </c>
-      <c r="N309" t="n">
+      <c r="N309" s="0" t="n">
         <v>-0.26</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
         <v>46311</v>
+      </c>
+      <c r="B310" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="I310" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K310" t="n">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="L310" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="M310" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="N310" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="311">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25753,51 +25753,92 @@
       <c r="A552" s="1" t="n">
         <v>46311</v>
       </c>
-      <c r="B552" t="n">
+      <c r="B552" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="C552" t="n">
+      <c r="C552" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="D552" t="n">
+      <c r="D552" s="0" t="n">
         <v>-7</v>
       </c>
-      <c r="E552" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F552" t="n">
+      <c r="E552" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F552" s="0" t="n">
         <v>-10.1</v>
       </c>
-      <c r="G552" t="n">
+      <c r="G552" s="0" t="n">
         <v>-5.9</v>
       </c>
-      <c r="H552" t="n">
+      <c r="H552" s="0" t="n">
         <v>-5.8</v>
       </c>
-      <c r="I552" t="n">
+      <c r="I552" s="0" t="n">
         <v>-7.2</v>
       </c>
-      <c r="J552" t="n">
+      <c r="J552" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="K552" t="n">
+      <c r="K552" s="0" t="n">
         <v>-14.6</v>
       </c>
-      <c r="L552" t="n">
+      <c r="L552" s="0" t="n">
         <v>-7.8</v>
       </c>
-      <c r="M552" t="n">
+      <c r="M552" s="0" t="n">
         <v>-6.8</v>
       </c>
-      <c r="N552" t="n">
+      <c r="N552" s="0" t="n">
         <v>-2.5</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="1" t="n">
         <v>46312</v>
+      </c>
+      <c r="B553" t="n">
+        <v>-8</v>
+      </c>
+      <c r="C553" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="D553" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F553" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="G553" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H553" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I553" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="J553" t="n">
+        <v>-21.4</v>
+      </c>
+      <c r="K553" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="L553" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="M553" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="N553" t="n">
+        <v>-6.3</v>
       </c>
     </row>
     <row r="554">
@@ -51896,51 +51937,92 @@
       <c r="A552" s="1" t="n">
         <v>46311</v>
       </c>
-      <c r="B552" t="n">
+      <c r="B552" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C552" t="n">
+      <c r="C552" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="D552" t="n">
+      <c r="D552" s="0" t="n">
         <v>-2.6</v>
       </c>
-      <c r="E552" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F552" t="n">
+      <c r="E552" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F552" s="0" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G552" t="n">
+      <c r="G552" s="0" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H552" t="n">
+      <c r="H552" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I552" t="n">
+      <c r="I552" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="J552" t="n">
+      <c r="J552" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="K552" t="n">
+      <c r="K552" s="0" t="n">
         <v>-6</v>
       </c>
-      <c r="L552" t="n">
+      <c r="L552" s="0" t="n">
         <v>-3.3</v>
       </c>
-      <c r="M552" t="n">
+      <c r="M552" s="0" t="n">
         <v>-3.2</v>
       </c>
-      <c r="N552" t="n">
+      <c r="N552" s="0" t="n">
         <v>7.1</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="1" t="n">
         <v>46312</v>
+      </c>
+      <c r="B553" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C553" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D553" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F553" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="G553" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="H553" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J553" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K553" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L553" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="M553" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="N553" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="554">
@@ -69185,59 +69267,106 @@
       <c r="A310" s="1" t="n">
         <v>46311</v>
       </c>
-      <c r="B310" t="n">
+      <c r="B310" s="0" t="n">
         <v>-0.58</v>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F310" t="n">
+      <c r="C310" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D310" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E310" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F310" s="0" t="n">
         <v>-6.8</v>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H310" t="n">
+      <c r="G310" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H310" s="0" t="n">
         <v>-2.18</v>
       </c>
-      <c r="I310" t="n">
+      <c r="I310" s="0" t="n">
         <v>-2.55</v>
       </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K310" t="n">
+      <c r="J310" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K310" s="0" t="n">
         <v>-9.550000000000001</v>
       </c>
-      <c r="L310" t="n">
+      <c r="L310" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="M310" t="n">
+      <c r="M310" s="0" t="n">
         <v>-5.59</v>
       </c>
-      <c r="N310" t="n">
+      <c r="N310" s="0" t="n">
         <v>0.91</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
         <v>46312</v>
+      </c>
+      <c r="B311" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>-13.99</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="I311" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="J311" t="n">
+        <v>-12.29</v>
+      </c>
+      <c r="K311" t="n">
+        <v>-16.78</v>
+      </c>
+      <c r="L311" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="M311" t="n">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="N311" t="n">
+        <v>-4.26</v>
       </c>
     </row>
     <row r="312">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25799,51 +25799,92 @@
       <c r="A553" s="1" t="n">
         <v>46312</v>
       </c>
-      <c r="B553" t="n">
+      <c r="B553" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="C553" t="n">
+      <c r="C553" s="0" t="n">
         <v>-10.7</v>
       </c>
-      <c r="D553" t="n">
+      <c r="D553" s="0" t="n">
         <v>-19.4</v>
       </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F553" t="n">
+      <c r="E553" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F553" s="0" t="n">
         <v>-20.9</v>
       </c>
-      <c r="G553" t="n">
+      <c r="G553" s="0" t="n">
         <v>-17</v>
       </c>
-      <c r="H553" t="n">
+      <c r="H553" s="0" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I553" t="n">
+      <c r="I553" s="0" t="n">
         <v>-9.4</v>
       </c>
-      <c r="J553" t="n">
+      <c r="J553" s="0" t="n">
         <v>-21.4</v>
       </c>
-      <c r="K553" t="n">
+      <c r="K553" s="0" t="n">
         <v>-25.7</v>
       </c>
-      <c r="L553" t="n">
+      <c r="L553" s="0" t="n">
         <v>-15.3</v>
       </c>
-      <c r="M553" t="n">
+      <c r="M553" s="0" t="n">
         <v>-16.9</v>
       </c>
-      <c r="N553" t="n">
+      <c r="N553" s="0" t="n">
         <v>-6.3</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="n">
         <v>46313</v>
+      </c>
+      <c r="B554" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C554" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="D554" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F554" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="G554" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="H554" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I554" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="J554" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="K554" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="L554" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="M554" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="N554" t="n">
+        <v>-9.9</v>
       </c>
     </row>
     <row r="555">
@@ -51983,51 +52024,92 @@
       <c r="A553" s="1" t="n">
         <v>46312</v>
       </c>
-      <c r="B553" t="n">
+      <c r="B553" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="C553" t="n">
+      <c r="C553" s="0" t="n">
         <v>1.6</v>
       </c>
-      <c r="D553" t="n">
+      <c r="D553" s="0" t="n">
         <v>-5.5</v>
       </c>
-      <c r="E553" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F553" t="n">
+      <c r="E553" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F553" s="0" t="n">
         <v>-7.5</v>
       </c>
-      <c r="G553" t="n">
+      <c r="G553" s="0" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H553" t="n">
+      <c r="H553" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="I553" t="n">
+      <c r="I553" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="J553" t="n">
+      <c r="J553" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="K553" t="n">
+      <c r="K553" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="L553" t="n">
+      <c r="L553" s="0" t="n">
         <v>-5.8</v>
       </c>
-      <c r="M553" t="n">
+      <c r="M553" s="0" t="n">
         <v>-4.4</v>
       </c>
-      <c r="N553" t="n">
+      <c r="N553" s="0" t="n">
         <v>-1.8</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="n">
         <v>46313</v>
+      </c>
+      <c r="B554" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C554" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D554" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F554" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="G554" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H554" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I554" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J554" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="K554" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L554" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="M554" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N554" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="555">
@@ -69321,57 +69403,104 @@
       <c r="A311" s="1" t="n">
         <v>46312</v>
       </c>
-      <c r="B311" t="n">
+      <c r="B311" s="0" t="n">
         <v>-2.44</v>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F311" t="n">
+      <c r="C311" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D311" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E311" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F311" s="0" t="n">
         <v>-13.99</v>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H311" t="n">
+      <c r="G311" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H311" s="0" t="n">
         <v>-2.34</v>
       </c>
-      <c r="I311" t="n">
+      <c r="I311" s="0" t="n">
         <v>-4.96</v>
       </c>
-      <c r="J311" t="n">
+      <c r="J311" s="0" t="n">
         <v>-12.29</v>
       </c>
-      <c r="K311" t="n">
+      <c r="K311" s="0" t="n">
         <v>-16.78</v>
       </c>
-      <c r="L311" t="n">
+      <c r="L311" s="0" t="n">
         <v>-10.79</v>
       </c>
-      <c r="M311" t="n">
+      <c r="M311" s="0" t="n">
         <v>-9.460000000000001</v>
       </c>
-      <c r="N311" t="n">
+      <c r="N311" s="0" t="n">
         <v>-4.26</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
         <v>46313</v>
+      </c>
+      <c r="B312" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>-10.74</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="I312" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="J312" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="K312" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="L312" t="n">
+        <v>-10.95</v>
+      </c>
+      <c r="M312" t="n">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="N312" t="n">
+        <v>-5.33</v>
       </c>
     </row>
     <row r="313">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25845,51 +25845,92 @@
       <c r="A554" s="1" t="n">
         <v>46313</v>
       </c>
-      <c r="B554" t="n">
+      <c r="B554" s="0" t="n">
         <v>-2.7</v>
       </c>
-      <c r="C554" t="n">
+      <c r="C554" s="0" t="n">
         <v>-4.5</v>
       </c>
-      <c r="D554" t="n">
+      <c r="D554" s="0" t="n">
         <v>-7.4</v>
       </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F554" t="n">
+      <c r="E554" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F554" s="0" t="n">
         <v>-14.8</v>
       </c>
-      <c r="G554" t="n">
+      <c r="G554" s="0" t="n">
         <v>-17.2</v>
       </c>
-      <c r="H554" t="n">
+      <c r="H554" s="0" t="n">
         <v>-12</v>
       </c>
-      <c r="I554" t="n">
+      <c r="I554" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="J554" t="n">
+      <c r="J554" s="0" t="n">
         <v>-12.1</v>
       </c>
-      <c r="K554" t="n">
+      <c r="K554" s="0" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="L554" t="n">
+      <c r="L554" s="0" t="n">
         <v>-15.6</v>
       </c>
-      <c r="M554" t="n">
+      <c r="M554" s="0" t="n">
         <v>-16.6</v>
       </c>
-      <c r="N554" t="n">
+      <c r="N554" s="0" t="n">
         <v>-9.9</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="1" t="n">
         <v>46314</v>
+      </c>
+      <c r="B555" t="n">
+        <v>-10</v>
+      </c>
+      <c r="C555" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="D555" t="n">
+        <v>-20</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F555" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="G555" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="H555" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I555" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="J555" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="K555" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="L555" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="M555" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="N555" t="n">
+        <v>-9.9</v>
       </c>
     </row>
     <row r="556">
@@ -52070,51 +52111,92 @@
       <c r="A554" s="1" t="n">
         <v>46313</v>
       </c>
-      <c r="B554" t="n">
+      <c r="B554" s="0" t="n">
         <v>4.3</v>
       </c>
-      <c r="C554" t="n">
+      <c r="C554" s="0" t="n">
         <v>1.4</v>
       </c>
-      <c r="D554" t="n">
+      <c r="D554" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F554" t="n">
+      <c r="E554" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F554" s="0" t="n">
         <v>-4.2</v>
       </c>
-      <c r="G554" t="n">
+      <c r="G554" s="0" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H554" t="n">
+      <c r="H554" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="I554" t="n">
+      <c r="I554" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="J554" t="n">
+      <c r="J554" s="0" t="n">
         <v>-3.6</v>
       </c>
-      <c r="K554" t="n">
+      <c r="K554" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="L554" t="n">
+      <c r="L554" s="0" t="n">
         <v>-5.6</v>
       </c>
-      <c r="M554" t="n">
+      <c r="M554" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="N554" t="n">
+      <c r="N554" s="0" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="1" t="n">
         <v>46314</v>
+      </c>
+      <c r="B555" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C555" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="D555" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F555" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G555" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="H555" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I555" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J555" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="K555" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L555" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="M555" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="N555" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="556">
@@ -69455,57 +69537,104 @@
       <c r="A312" s="1" t="n">
         <v>46313</v>
       </c>
-      <c r="B312" t="n">
+      <c r="B312" s="0" t="n">
         <v>-0.58</v>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F312" t="n">
+      <c r="C312" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D312" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E312" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F312" s="0" t="n">
         <v>-10.74</v>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H312" t="n">
+      <c r="G312" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H312" s="0" t="n">
         <v>-6.54</v>
       </c>
-      <c r="I312" t="n">
+      <c r="I312" s="0" t="n">
         <v>-1.23</v>
       </c>
-      <c r="J312" t="n">
+      <c r="J312" s="0" t="n">
         <v>-7.93</v>
       </c>
-      <c r="K312" t="n">
+      <c r="K312" s="0" t="n">
         <v>-7.13</v>
       </c>
-      <c r="L312" t="n">
+      <c r="L312" s="0" t="n">
         <v>-10.95</v>
       </c>
-      <c r="M312" t="n">
+      <c r="M312" s="0" t="n">
         <v>-9.960000000000001</v>
       </c>
-      <c r="N312" t="n">
+      <c r="N312" s="0" t="n">
         <v>-5.33</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
         <v>46314</v>
+      </c>
+      <c r="B313" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="I313" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="J313" t="n">
+        <v>-10.68</v>
+      </c>
+      <c r="K313" t="n">
+        <v>-16.51</v>
+      </c>
+      <c r="L313" t="n">
+        <v>-10.01</v>
+      </c>
+      <c r="M313" t="n">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="N313" t="n">
+        <v>-5.98</v>
       </c>
     </row>
     <row r="314">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25891,45 +25891,45 @@
       <c r="A555" s="1" t="n">
         <v>46314</v>
       </c>
-      <c r="B555" t="n">
+      <c r="B555" s="0" t="n">
         <v>-10</v>
       </c>
-      <c r="C555" t="n">
+      <c r="C555" s="0" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="D555" t="n">
+      <c r="D555" s="0" t="n">
         <v>-20</v>
       </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F555" t="n">
+      <c r="E555" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F555" s="0" t="n">
         <v>-20.5</v>
       </c>
-      <c r="G555" t="n">
+      <c r="G555" s="0" t="n">
         <v>-13.8</v>
       </c>
-      <c r="H555" t="n">
+      <c r="H555" s="0" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="I555" t="n">
+      <c r="I555" s="0" t="n">
         <v>-6.7</v>
       </c>
-      <c r="J555" t="n">
+      <c r="J555" s="0" t="n">
         <v>-19.4</v>
       </c>
-      <c r="K555" t="n">
+      <c r="K555" s="0" t="n">
         <v>-25.1</v>
       </c>
-      <c r="L555" t="n">
+      <c r="L555" s="0" t="n">
         <v>-16.3</v>
       </c>
-      <c r="M555" t="n">
+      <c r="M555" s="0" t="n">
         <v>-16.7</v>
       </c>
-      <c r="N555" t="n">
+      <c r="N555" s="0" t="n">
         <v>-9.9</v>
       </c>
     </row>
@@ -25937,10 +25937,90 @@
       <c r="A556" s="1" t="n">
         <v>46315</v>
       </c>
+      <c r="B556" s="0" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="C556" s="0" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="D556" s="0" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="E556" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F556" s="0" t="n">
+        <v>-26.7</v>
+      </c>
+      <c r="G556" s="0" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="H556" s="0" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="I556" s="0" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="J556" s="0" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="K556" s="0" t="n">
+        <v>-31.1</v>
+      </c>
+      <c r="L556" s="0" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="M556" s="0" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="N556" s="0" t="n">
+        <v>-10.4</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="1" t="n">
         <v>46316</v>
+      </c>
+      <c r="B557" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="C557" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="D557" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E557" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F557" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="G557" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="H557" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="I557" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="J557" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="K557" t="n">
+        <v>-22.6</v>
+      </c>
+      <c r="L557" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="M557" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="N557" t="n">
+        <v>-9.6</v>
       </c>
     </row>
     <row r="558">
@@ -52157,45 +52237,45 @@
       <c r="A555" s="1" t="n">
         <v>46314</v>
       </c>
-      <c r="B555" t="n">
+      <c r="B555" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="C555" t="n">
+      <c r="C555" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="D555" t="n">
+      <c r="D555" s="0" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E555" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F555" t="n">
+      <c r="E555" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F555" s="0" t="n">
         <v>-7</v>
       </c>
-      <c r="G555" t="n">
+      <c r="G555" s="0" t="n">
         <v>-4.3</v>
       </c>
-      <c r="H555" t="n">
+      <c r="H555" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="I555" t="n">
+      <c r="I555" s="0" t="n">
         <v>2.9</v>
       </c>
-      <c r="J555" t="n">
+      <c r="J555" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="K555" t="n">
+      <c r="K555" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="L555" t="n">
+      <c r="L555" s="0" t="n">
         <v>-6.3</v>
       </c>
-      <c r="M555" t="n">
+      <c r="M555" s="0" t="n">
         <v>-5.6</v>
       </c>
-      <c r="N555" t="n">
+      <c r="N555" s="0" t="n">
         <v>-1.1</v>
       </c>
     </row>
@@ -52203,10 +52283,90 @@
       <c r="A556" s="1" t="n">
         <v>46315</v>
       </c>
+      <c r="B556" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C556" s="0" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="D556" s="0" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="E556" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F556" s="0" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="G556" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H556" s="0" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I556" s="0" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J556" s="0" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="K556" s="0" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="L556" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M556" s="0" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="N556" s="0" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="1" t="n">
         <v>46316</v>
+      </c>
+      <c r="B557" t="n">
+        <v>3</v>
+      </c>
+      <c r="C557" t="n">
+        <v>2</v>
+      </c>
+      <c r="D557" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E557" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="F557" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="G557" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H557" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I557" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J557" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K557" t="n">
+        <v>2</v>
+      </c>
+      <c r="L557" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="M557" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N557" t="n">
+        <v>9.4</v>
       </c>
     </row>
     <row r="558">
@@ -69589,51 +69749,51 @@
       <c r="A313" s="1" t="n">
         <v>46314</v>
       </c>
-      <c r="B313" t="n">
+      <c r="B313" s="0" t="n">
         <v>-2.45</v>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F313" t="n">
+      <c r="C313" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D313" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E313" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F313" s="0" t="n">
         <v>-13.84</v>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H313" t="n">
+      <c r="G313" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H313" s="0" t="n">
         <v>-3.94</v>
       </c>
-      <c r="I313" t="n">
+      <c r="I313" s="0" t="n">
         <v>-2.45</v>
       </c>
-      <c r="J313" t="n">
+      <c r="J313" s="0" t="n">
         <v>-10.68</v>
       </c>
-      <c r="K313" t="n">
+      <c r="K313" s="0" t="n">
         <v>-16.51</v>
       </c>
-      <c r="L313" t="n">
+      <c r="L313" s="0" t="n">
         <v>-10.01</v>
       </c>
-      <c r="M313" t="n">
+      <c r="M313" s="0" t="n">
         <v>-9.880000000000001</v>
       </c>
-      <c r="N313" t="n">
+      <c r="N313" s="0" t="n">
         <v>-5.98</v>
       </c>
     </row>
@@ -69641,10 +69801,104 @@
       <c r="A314" s="1" t="n">
         <v>46315</v>
       </c>
+      <c r="B314" s="0" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="C314" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D314" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E314" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F314" s="0" t="n">
+        <v>-20.48</v>
+      </c>
+      <c r="G314" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H314" s="0" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="I314" s="0" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="J314" s="0" t="n">
+        <v>-16.26</v>
+      </c>
+      <c r="K314" s="0" t="n">
+        <v>-22.06</v>
+      </c>
+      <c r="L314" s="0" t="n">
+        <v>-15.25</v>
+      </c>
+      <c r="M314" s="0" t="n">
+        <v>-12.85</v>
+      </c>
+      <c r="N314" s="0" t="n">
+        <v>-5.62</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
         <v>46316</v>
+      </c>
+      <c r="B315" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>-3.78</v>
+      </c>
+      <c r="I315" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="J315" t="n">
+        <v>-10.84</v>
+      </c>
+      <c r="K315" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="L315" t="n">
+        <v>-14.69</v>
+      </c>
+      <c r="M315" t="n">
+        <v>-10.65</v>
+      </c>
+      <c r="N315" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="316">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -25983,43 +25983,43 @@
       <c r="A557" s="1" t="n">
         <v>46316</v>
       </c>
-      <c r="B557" t="n">
+      <c r="B557" s="0" t="n">
         <v>-9.5</v>
       </c>
-      <c r="C557" t="n">
+      <c r="C557" s="0" t="n">
         <v>-12.3</v>
       </c>
-      <c r="D557" t="n">
+      <c r="D557" s="0" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="E557" t="n">
+      <c r="E557" s="0" t="n">
         <v>-21</v>
       </c>
-      <c r="F557" t="n">
+      <c r="F557" s="0" t="n">
         <v>-25.7</v>
       </c>
-      <c r="G557" t="n">
+      <c r="G557" s="0" t="n">
         <v>-16.5</v>
       </c>
-      <c r="H557" t="n">
+      <c r="H557" s="0" t="n">
         <v>-11.2</v>
       </c>
-      <c r="I557" t="n">
+      <c r="I557" s="0" t="n">
         <v>-7.9</v>
       </c>
-      <c r="J557" t="n">
+      <c r="J557" s="0" t="n">
         <v>-18.1</v>
       </c>
-      <c r="K557" t="n">
+      <c r="K557" s="0" t="n">
         <v>-22.6</v>
       </c>
-      <c r="L557" t="n">
+      <c r="L557" s="0" t="n">
         <v>-20.6</v>
       </c>
-      <c r="M557" t="n">
+      <c r="M557" s="0" t="n">
         <v>-18.9</v>
       </c>
-      <c r="N557" t="n">
+      <c r="N557" s="0" t="n">
         <v>-9.6</v>
       </c>
     </row>
@@ -26027,10 +26027,92 @@
       <c r="A558" s="1" t="n">
         <v>46317</v>
       </c>
+      <c r="B558" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C558" s="0" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D558" s="0" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="E558" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F558" s="0" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="G558" s="0" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="H558" s="0" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="I558" s="0" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="J558" s="0" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="K558" s="0" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="L558" s="0" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="M558" s="0" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="N558" s="0" t="n">
+        <v>-1.3</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="1" t="n">
         <v>46318</v>
+      </c>
+      <c r="B559" t="n">
+        <v>-8</v>
+      </c>
+      <c r="C559" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="D559" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F559" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="G559" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H559" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="I559" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="J559" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="K559" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="L559" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="M559" t="n">
+        <v>-14</v>
+      </c>
+      <c r="N559" t="n">
+        <v>-6.9</v>
       </c>
     </row>
     <row r="560">
@@ -52329,43 +52411,43 @@
       <c r="A557" s="1" t="n">
         <v>46316</v>
       </c>
-      <c r="B557" t="n">
+      <c r="B557" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C557" t="n">
+      <c r="C557" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D557" t="n">
+      <c r="D557" s="0" t="n">
         <v>3.1</v>
       </c>
-      <c r="E557" t="n">
+      <c r="E557" s="0" t="n">
         <v>-6.8</v>
       </c>
-      <c r="F557" t="n">
+      <c r="F557" s="0" t="n">
         <v>-7.5</v>
       </c>
-      <c r="G557" t="n">
+      <c r="G557" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="H557" t="n">
+      <c r="H557" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="I557" t="n">
+      <c r="I557" s="0" t="n">
         <v>0.9</v>
       </c>
-      <c r="J557" t="n">
+      <c r="J557" s="0" t="n">
         <v>-4.4</v>
       </c>
-      <c r="K557" t="n">
+      <c r="K557" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L557" t="n">
+      <c r="L557" s="0" t="n">
         <v>-7.1</v>
       </c>
-      <c r="M557" t="n">
+      <c r="M557" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="N557" t="n">
+      <c r="N557" s="0" t="n">
         <v>9.4</v>
       </c>
     </row>
@@ -52373,10 +52455,92 @@
       <c r="A558" s="1" t="n">
         <v>46317</v>
       </c>
+      <c r="B558" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C558" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D558" s="0" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E558" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F558" s="0" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G558" s="0" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="H558" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I558" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J558" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K558" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L558" s="0" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="M558" s="0" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="N558" s="0" t="n">
+        <v>6.7</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="1" t="n">
         <v>46318</v>
+      </c>
+      <c r="B559" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C559" t="n">
+        <v>4</v>
+      </c>
+      <c r="D559" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F559" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="G559" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="H559" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I559" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J559" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="K559" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="L559" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="M559" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N559" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="560">
@@ -69853,51 +70017,51 @@
       <c r="A315" s="1" t="n">
         <v>46316</v>
       </c>
-      <c r="B315" t="n">
+      <c r="B315" s="0" t="n">
         <v>-3.85</v>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F315" t="n">
+      <c r="C315" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D315" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E315" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F315" s="0" t="n">
         <v>-18.3</v>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H315" t="n">
+      <c r="G315" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H315" s="0" t="n">
         <v>-3.78</v>
       </c>
-      <c r="I315" t="n">
+      <c r="I315" s="0" t="n">
         <v>-3.99</v>
       </c>
-      <c r="J315" t="n">
+      <c r="J315" s="0" t="n">
         <v>-10.84</v>
       </c>
-      <c r="K315" t="n">
+      <c r="K315" s="0" t="n">
         <v>-3.28</v>
       </c>
-      <c r="L315" t="n">
+      <c r="L315" s="0" t="n">
         <v>-14.69</v>
       </c>
-      <c r="M315" t="n">
+      <c r="M315" s="0" t="n">
         <v>-10.65</v>
       </c>
-      <c r="N315" t="n">
+      <c r="N315" s="0" t="n">
         <v>-1.59</v>
       </c>
     </row>
@@ -69905,10 +70069,104 @@
       <c r="A316" s="1" t="n">
         <v>46317</v>
       </c>
+      <c r="B316" s="0" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="C316" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D316" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E316" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F316" s="0" t="n">
+        <v>-6.63</v>
+      </c>
+      <c r="G316" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H316" s="0" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="I316" s="0" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="J316" s="0" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="K316" s="0" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="L316" s="0" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="M316" s="0" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="N316" s="0" t="n">
+        <v>0.76</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
         <v>46318</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="I317" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J317" t="n">
+        <v>-10.84</v>
+      </c>
+      <c r="K317" t="n">
+        <v>-7.34</v>
+      </c>
+      <c r="L317" t="n">
+        <v>-9.06</v>
+      </c>
+      <c r="M317" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="N317" t="n">
+        <v>-3.26</v>
       </c>
     </row>
     <row r="318">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -26073,51 +26073,90 @@
       <c r="A559" s="1" t="n">
         <v>46318</v>
       </c>
-      <c r="B559" t="n">
+      <c r="B559" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="C559" t="n">
+      <c r="C559" s="0" t="n">
         <v>-6.1</v>
       </c>
-      <c r="D559" t="n">
+      <c r="D559" s="0" t="n">
         <v>-15.7</v>
       </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F559" t="n">
+      <c r="E559" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F559" s="0" t="n">
         <v>-20.7</v>
       </c>
-      <c r="G559" t="n">
+      <c r="G559" s="0" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H559" t="n">
+      <c r="H559" s="0" t="n">
         <v>-3.9</v>
       </c>
-      <c r="I559" t="n">
+      <c r="I559" s="0" t="n">
         <v>-5.7</v>
       </c>
-      <c r="J559" t="n">
+      <c r="J559" s="0" t="n">
         <v>-15.2</v>
       </c>
-      <c r="K559" t="n">
+      <c r="K559" s="0" t="n">
         <v>-13.3</v>
       </c>
-      <c r="L559" t="n">
+      <c r="L559" s="0" t="n">
         <v>-14.7</v>
       </c>
-      <c r="M559" t="n">
+      <c r="M559" s="0" t="n">
         <v>-14</v>
       </c>
-      <c r="N559" t="n">
+      <c r="N559" s="0" t="n">
         <v>-6.9</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="1" t="n">
         <v>46319</v>
+      </c>
+      <c r="B560" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="C560" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="D560" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="E560" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="F560" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="G560" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="H560" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="I560" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="J560" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K560" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="L560" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="M560" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="N560" t="n">
+        <v>-11.1</v>
       </c>
     </row>
     <row r="561">
@@ -52501,51 +52540,90 @@
       <c r="A559" s="1" t="n">
         <v>46318</v>
       </c>
-      <c r="B559" t="n">
+      <c r="B559" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="C559" t="n">
+      <c r="C559" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="D559" t="n">
+      <c r="D559" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F559" t="n">
+      <c r="E559" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F559" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="G559" t="n">
+      <c r="G559" s="0" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H559" t="n">
+      <c r="H559" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="I559" t="n">
+      <c r="I559" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="J559" t="n">
+      <c r="J559" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="K559" t="n">
+      <c r="K559" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="L559" t="n">
+      <c r="L559" s="0" t="n">
         <v>-1.2</v>
       </c>
-      <c r="M559" t="n">
+      <c r="M559" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="N559" t="n">
+      <c r="N559" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="1" t="n">
         <v>46319</v>
+      </c>
+      <c r="B560" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C560" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D560" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="E560" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="F560" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="G560" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="H560" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I560" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J560" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K560" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L560" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="M560" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="N560" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="561">
@@ -70121,57 +70199,104 @@
       <c r="A317" s="1" t="n">
         <v>46318</v>
       </c>
-      <c r="B317" t="n">
+      <c r="B317" s="0" t="n">
         <v>-2.46</v>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F317" t="n">
+      <c r="C317" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D317" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E317" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F317" s="0" t="n">
         <v>-14.29</v>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H317" t="n">
+      <c r="G317" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H317" s="0" t="n">
         <v>-0.51</v>
       </c>
-      <c r="I317" t="n">
+      <c r="I317" s="0" t="n">
         <v>-0.88</v>
       </c>
-      <c r="J317" t="n">
+      <c r="J317" s="0" t="n">
         <v>-10.84</v>
       </c>
-      <c r="K317" t="n">
+      <c r="K317" s="0" t="n">
         <v>-7.34</v>
       </c>
-      <c r="L317" t="n">
+      <c r="L317" s="0" t="n">
         <v>-9.06</v>
       </c>
-      <c r="M317" t="n">
+      <c r="M317" s="0" t="n">
         <v>-8.59</v>
       </c>
-      <c r="N317" t="n">
+      <c r="N317" s="0" t="n">
         <v>-3.26</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
         <v>46319</v>
+      </c>
+      <c r="B318" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="I318" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="J318" t="n">
+        <v>-14.54</v>
+      </c>
+      <c r="K318" t="n">
+        <v>-14.74</v>
+      </c>
+      <c r="L318" t="n">
+        <v>-12.54</v>
+      </c>
+      <c r="M318" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="N318" t="n">
+        <v>-5.56</v>
       </c>
     </row>
     <row r="319">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -26119,49 +26119,88 @@
       <c r="A560" s="1" t="n">
         <v>46319</v>
       </c>
-      <c r="B560" t="n">
+      <c r="B560" s="0" t="n">
         <v>-9.4</v>
       </c>
-      <c r="C560" t="n">
+      <c r="C560" s="0" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="D560" t="n">
+      <c r="D560" s="0" t="n">
         <v>-20.4</v>
       </c>
-      <c r="E560" t="n">
+      <c r="E560" s="0" t="n">
         <v>-15.8</v>
       </c>
-      <c r="F560" t="n">
+      <c r="F560" s="0" t="n">
         <v>-20.6</v>
       </c>
-      <c r="G560" t="n">
+      <c r="G560" s="0" t="n">
         <v>-13.7</v>
       </c>
-      <c r="H560" t="n">
+      <c r="H560" s="0" t="n">
         <v>-12.1</v>
       </c>
-      <c r="I560" t="n">
+      <c r="I560" s="0" t="n">
         <v>-7.4</v>
       </c>
-      <c r="J560" t="n">
+      <c r="J560" s="0" t="n">
         <v>-21</v>
       </c>
-      <c r="K560" t="n">
+      <c r="K560" s="0" t="n">
         <v>-22.2</v>
       </c>
-      <c r="L560" t="n">
+      <c r="L560" s="0" t="n">
         <v>-18.5</v>
       </c>
-      <c r="M560" t="n">
+      <c r="M560" s="0" t="n">
         <v>-12.9</v>
       </c>
-      <c r="N560" t="n">
+      <c r="N560" s="0" t="n">
         <v>-11.1</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="1" t="n">
         <v>46320</v>
+      </c>
+      <c r="B561" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="C561" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="D561" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="E561" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F561" t="n">
+        <v>-24</v>
+      </c>
+      <c r="G561" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="H561" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="I561" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="J561" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="K561" t="n">
+        <v>-24.7</v>
+      </c>
+      <c r="L561" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="M561" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="N561" t="n">
+        <v>-10.7</v>
       </c>
     </row>
     <row r="562">
@@ -52586,49 +52625,88 @@
       <c r="A560" s="1" t="n">
         <v>46319</v>
       </c>
-      <c r="B560" t="n">
+      <c r="B560" s="0" t="n">
         <v>4.4</v>
       </c>
-      <c r="C560" t="n">
+      <c r="C560" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="D560" t="n">
+      <c r="D560" s="0" t="n">
         <v>-6.5</v>
       </c>
-      <c r="E560" t="n">
+      <c r="E560" s="0" t="n">
         <v>-4.6</v>
       </c>
-      <c r="F560" t="n">
+      <c r="F560" s="0" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="G560" t="n">
+      <c r="G560" s="0" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H560" t="n">
+      <c r="H560" s="0" t="n">
         <v>2.6</v>
       </c>
-      <c r="I560" t="n">
+      <c r="I560" s="0" t="n">
         <v>3.6</v>
       </c>
-      <c r="J560" t="n">
+      <c r="J560" s="0" t="n">
         <v>-7</v>
       </c>
-      <c r="K560" t="n">
+      <c r="K560" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="L560" t="n">
+      <c r="L560" s="0" t="n">
         <v>-3.2</v>
       </c>
-      <c r="M560" t="n">
+      <c r="M560" s="0" t="n">
         <v>-3.8</v>
       </c>
-      <c r="N560" t="n">
+      <c r="N560" s="0" t="n">
         <v>2.2</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="1" t="n">
         <v>46320</v>
+      </c>
+      <c r="B561" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C561" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D561" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="E561" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="F561" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="G561" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="H561" t="n">
+        <v>2</v>
+      </c>
+      <c r="I561" t="n">
+        <v>3</v>
+      </c>
+      <c r="J561" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K561" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="L561" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="M561" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="N561" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="562">
@@ -70251,57 +70329,104 @@
       <c r="A318" s="1" t="n">
         <v>46319</v>
       </c>
-      <c r="B318" t="n">
+      <c r="B318" s="0" t="n">
         <v>-3.79</v>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F318" t="n">
+      <c r="C318" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D318" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E318" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F318" s="0" t="n">
         <v>-13.84</v>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H318" t="n">
+      <c r="G318" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H318" s="0" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I318" t="n">
+      <c r="I318" s="0" t="n">
         <v>-2.58</v>
       </c>
-      <c r="J318" t="n">
+      <c r="J318" s="0" t="n">
         <v>-14.54</v>
       </c>
-      <c r="K318" t="n">
+      <c r="K318" s="0" t="n">
         <v>-14.74</v>
       </c>
-      <c r="L318" t="n">
+      <c r="L318" s="0" t="n">
         <v>-12.54</v>
       </c>
-      <c r="M318" t="n">
+      <c r="M318" s="0" t="n">
         <v>-9.130000000000001</v>
       </c>
-      <c r="N318" t="n">
+      <c r="N318" s="0" t="n">
         <v>-5.56</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
         <v>46320</v>
+      </c>
+      <c r="B319" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>-17.93</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="I319" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="J319" t="n">
+        <v>-10.73</v>
+      </c>
+      <c r="K319" t="n">
+        <v>-15.45</v>
+      </c>
+      <c r="L319" t="n">
+        <v>-12.43</v>
+      </c>
+      <c r="M319" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="N319" t="n">
+        <v>-5.44</v>
       </c>
     </row>
     <row r="320">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -26163,49 +26163,90 @@
       <c r="A561" s="1" t="n">
         <v>46320</v>
       </c>
-      <c r="B561" t="n">
+      <c r="B561" s="0" t="n">
         <v>-10.9</v>
       </c>
-      <c r="C561" t="n">
+      <c r="C561" s="0" t="n">
         <v>-11.8</v>
       </c>
-      <c r="D561" t="n">
+      <c r="D561" s="0" t="n">
         <v>-21.1</v>
       </c>
-      <c r="E561" t="n">
+      <c r="E561" s="0" t="n">
         <v>-20</v>
       </c>
-      <c r="F561" t="n">
+      <c r="F561" s="0" t="n">
         <v>-24</v>
       </c>
-      <c r="G561" t="n">
+      <c r="G561" s="0" t="n">
         <v>-15.8</v>
       </c>
-      <c r="H561" t="n">
+      <c r="H561" s="0" t="n">
         <v>-10.1</v>
       </c>
-      <c r="I561" t="n">
+      <c r="I561" s="0" t="n">
         <v>-9.1</v>
       </c>
-      <c r="J561" t="n">
+      <c r="J561" s="0" t="n">
         <v>-20.5</v>
       </c>
-      <c r="K561" t="n">
+      <c r="K561" s="0" t="n">
         <v>-24.7</v>
       </c>
-      <c r="L561" t="n">
+      <c r="L561" s="0" t="n">
         <v>-19.6</v>
       </c>
-      <c r="M561" t="n">
+      <c r="M561" s="0" t="n">
         <v>-16.2</v>
       </c>
-      <c r="N561" t="n">
+      <c r="N561" s="0" t="n">
         <v>-10.7</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="1" t="n">
         <v>46321</v>
+      </c>
+      <c r="B562" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="C562" t="n">
+        <v>-11</v>
+      </c>
+      <c r="D562" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F562" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="G562" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="H562" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I562" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="J562" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="K562" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="L562" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="M562" t="n">
+        <v>-18</v>
+      </c>
+      <c r="N562" t="n">
+        <v>-8.6</v>
       </c>
     </row>
     <row r="563">
@@ -52669,49 +52710,90 @@
       <c r="A561" s="1" t="n">
         <v>46320</v>
       </c>
-      <c r="B561" t="n">
+      <c r="B561" s="0" t="n">
         <v>2.3</v>
       </c>
-      <c r="C561" t="n">
+      <c r="C561" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="D561" t="n">
+      <c r="D561" s="0" t="n">
         <v>-6.6</v>
       </c>
-      <c r="E561" t="n">
+      <c r="E561" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="F561" t="n">
+      <c r="F561" s="0" t="n">
         <v>-10.2</v>
       </c>
-      <c r="G561" t="n">
+      <c r="G561" s="0" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H561" t="n">
+      <c r="H561" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I561" t="n">
+      <c r="I561" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J561" t="n">
+      <c r="J561" s="0" t="n">
         <v>-3</v>
       </c>
-      <c r="K561" t="n">
+      <c r="K561" s="0" t="n">
         <v>-7.5</v>
       </c>
-      <c r="L561" t="n">
+      <c r="L561" s="0" t="n">
         <v>-4.6</v>
       </c>
-      <c r="M561" t="n">
+      <c r="M561" s="0" t="n">
         <v>-3.9</v>
       </c>
-      <c r="N561" t="n">
+      <c r="N561" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="1" t="n">
         <v>46321</v>
+      </c>
+      <c r="B562" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C562" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D562" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F562" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="G562" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H562" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I562" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J562" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="K562" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L562" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="M562" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N562" t="n">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="563">
@@ -70381,57 +70463,104 @@
       <c r="A319" s="1" t="n">
         <v>46320</v>
       </c>
-      <c r="B319" t="n">
+      <c r="B319" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F319" t="n">
+      <c r="C319" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D319" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E319" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F319" s="0" t="n">
         <v>-17.93</v>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H319" t="n">
+      <c r="G319" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H319" s="0" t="n">
         <v>-4.01</v>
       </c>
-      <c r="I319" t="n">
+      <c r="I319" s="0" t="n">
         <v>-2.86</v>
       </c>
-      <c r="J319" t="n">
+      <c r="J319" s="0" t="n">
         <v>-10.73</v>
       </c>
-      <c r="K319" t="n">
+      <c r="K319" s="0" t="n">
         <v>-15.45</v>
       </c>
-      <c r="L319" t="n">
+      <c r="L319" s="0" t="n">
         <v>-12.43</v>
       </c>
-      <c r="M319" t="n">
+      <c r="M319" s="0" t="n">
         <v>-11.2</v>
       </c>
-      <c r="N319" t="n">
+      <c r="N319" s="0" t="n">
         <v>-5.44</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
         <v>46321</v>
+      </c>
+      <c r="B320" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>-12.01</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="I320" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="J320" t="n">
+        <v>-8.16</v>
+      </c>
+      <c r="K320" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="L320" t="n">
+        <v>-7.34</v>
+      </c>
+      <c r="M320" t="n">
+        <v>-10.41</v>
+      </c>
+      <c r="N320" t="n">
+        <v>-6.1</v>
       </c>
     </row>
     <row r="321">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -26207,51 +26207,90 @@
       <c r="A562" s="1" t="n">
         <v>46321</v>
       </c>
-      <c r="B562" t="n">
+      <c r="B562" s="0" t="n">
         <v>-10.6</v>
       </c>
-      <c r="C562" t="n">
+      <c r="C562" s="0" t="n">
         <v>-11</v>
       </c>
-      <c r="D562" t="n">
+      <c r="D562" s="0" t="n">
         <v>-18.3</v>
       </c>
-      <c r="E562" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F562" t="n">
+      <c r="E562" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F562" s="0" t="n">
         <v>-19.8</v>
       </c>
-      <c r="G562" t="n">
+      <c r="G562" s="0" t="n">
         <v>-12.3</v>
       </c>
-      <c r="H562" t="n">
+      <c r="H562" s="0" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I562" t="n">
+      <c r="I562" s="0" t="n">
         <v>-7.8</v>
       </c>
-      <c r="J562" t="n">
+      <c r="J562" s="0" t="n">
         <v>-13.4</v>
       </c>
-      <c r="K562" t="n">
+      <c r="K562" s="0" t="n">
         <v>-15.1</v>
       </c>
-      <c r="L562" t="n">
+      <c r="L562" s="0" t="n">
         <v>-10.4</v>
       </c>
-      <c r="M562" t="n">
+      <c r="M562" s="0" t="n">
         <v>-18</v>
       </c>
-      <c r="N562" t="n">
+      <c r="N562" s="0" t="n">
         <v>-8.6</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="1" t="n">
         <v>46322</v>
+      </c>
+      <c r="B563" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="C563" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="D563" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="E563" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="F563" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="G563" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="H563" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="I563" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="J563" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="K563" t="n">
+        <v>-24.6</v>
+      </c>
+      <c r="L563" t="n">
+        <v>-21</v>
+      </c>
+      <c r="M563" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="N563" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="564">
@@ -52754,51 +52793,90 @@
       <c r="A562" s="1" t="n">
         <v>46321</v>
       </c>
-      <c r="B562" t="n">
+      <c r="B562" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="C562" t="n">
+      <c r="C562" s="0" t="n">
         <v>3.5</v>
       </c>
-      <c r="D562" t="n">
+      <c r="D562" s="0" t="n">
         <v>-3.2</v>
       </c>
-      <c r="E562" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F562" t="n">
+      <c r="E562" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F562" s="0" t="n">
         <v>-6.1</v>
       </c>
-      <c r="G562" t="n">
+      <c r="G562" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="H562" t="n">
+      <c r="H562" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="I562" t="n">
+      <c r="I562" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="J562" t="n">
+      <c r="J562" s="0" t="n">
         <v>-4.2</v>
       </c>
-      <c r="K562" t="n">
+      <c r="K562" s="0" t="n">
         <v>-7</v>
       </c>
-      <c r="L562" t="n">
+      <c r="L562" s="0" t="n">
         <v>-4.3</v>
       </c>
-      <c r="M562" t="n">
+      <c r="M562" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="N562" t="n">
+      <c r="N562" s="0" t="n">
         <v>-3.2</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="1" t="n">
         <v>46322</v>
+      </c>
+      <c r="B563" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C563" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D563" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="E563" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F563" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="G563" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H563" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I563" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J563" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="K563" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="L563" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="M563" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="N563" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="564">
@@ -70515,57 +70593,104 @@
       <c r="A320" s="1" t="n">
         <v>46321</v>
       </c>
-      <c r="B320" t="n">
+      <c r="B320" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F320" t="n">
+      <c r="C320" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D320" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E320" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F320" s="0" t="n">
         <v>-12.01</v>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H320" t="n">
+      <c r="G320" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H320" s="0" t="n">
         <v>-3.01</v>
       </c>
-      <c r="I320" t="n">
+      <c r="I320" s="0" t="n">
         <v>-2.91</v>
       </c>
-      <c r="J320" t="n">
+      <c r="J320" s="0" t="n">
         <v>-8.16</v>
       </c>
-      <c r="K320" t="n">
+      <c r="K320" s="0" t="n">
         <v>-10.9</v>
       </c>
-      <c r="L320" t="n">
+      <c r="L320" s="0" t="n">
         <v>-7.34</v>
       </c>
-      <c r="M320" t="n">
+      <c r="M320" s="0" t="n">
         <v>-10.41</v>
       </c>
-      <c r="N320" t="n">
+      <c r="N320" s="0" t="n">
         <v>-6.1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
         <v>46322</v>
+      </c>
+      <c r="B321" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>-18.13</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="I321" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="J321" t="n">
+        <v>-16.28</v>
+      </c>
+      <c r="K321" t="n">
+        <v>-16.45</v>
+      </c>
+      <c r="L321" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="M321" t="n">
+        <v>-13.75</v>
+      </c>
+      <c r="N321" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="322">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -26253,43 +26253,43 @@
       <c r="A563" s="1" t="n">
         <v>46322</v>
       </c>
-      <c r="B563" t="n">
+      <c r="B563" s="0" t="n">
         <v>-12.2</v>
       </c>
-      <c r="C563" t="n">
+      <c r="C563" s="0" t="n">
         <v>-14.3</v>
       </c>
-      <c r="D563" t="n">
+      <c r="D563" s="0" t="n">
         <v>-20.2</v>
       </c>
-      <c r="E563" t="n">
+      <c r="E563" s="0" t="n">
         <v>-20.6</v>
       </c>
-      <c r="F563" t="n">
+      <c r="F563" s="0" t="n">
         <v>-25.2</v>
       </c>
-      <c r="G563" t="n">
+      <c r="G563" s="0" t="n">
         <v>-19.2</v>
       </c>
-      <c r="H563" t="n">
+      <c r="H563" s="0" t="n">
         <v>-14.1</v>
       </c>
-      <c r="I563" t="n">
+      <c r="I563" s="0" t="n">
         <v>-8.9</v>
       </c>
-      <c r="J563" t="n">
+      <c r="J563" s="0" t="n">
         <v>-24.8</v>
       </c>
-      <c r="K563" t="n">
+      <c r="K563" s="0" t="n">
         <v>-24.6</v>
       </c>
-      <c r="L563" t="n">
+      <c r="L563" s="0" t="n">
         <v>-21</v>
       </c>
-      <c r="M563" t="n">
+      <c r="M563" s="0" t="n">
         <v>-21.8</v>
       </c>
-      <c r="N563" t="n">
+      <c r="N563" s="0" t="n">
         <v>-12</v>
       </c>
     </row>
@@ -26297,15 +26297,134 @@
       <c r="A564" s="1" t="n">
         <v>46323</v>
       </c>
+      <c r="B564" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="C564" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D564" s="0" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E564" s="0" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="F564" s="0" t="n">
+        <v>-21</v>
+      </c>
+      <c r="G564" s="0" t="n">
+        <v>-13.7</v>
+      </c>
+      <c r="H564" s="0" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="I564" s="0" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="J564" s="0" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="K564" s="0" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="L564" s="0" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="M564" s="0" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="N564" s="0" t="n">
+        <v>-9.9</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="1" t="n">
         <v>46324</v>
       </c>
+      <c r="B565" s="0" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="C565" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="D565" s="0" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="E565" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F565" s="0" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="G565" s="0" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H565" s="0" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I565" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J565" s="0" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K565" s="0" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L565" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="M565" s="0" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="N565" s="0" t="n">
+        <v>-5.4</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="1" t="n">
         <v>46325</v>
+      </c>
+      <c r="B566" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="C566" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="D566" t="n">
+        <v>-18</v>
+      </c>
+      <c r="E566" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="F566" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="G566" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="H566" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="I566" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="J566" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="K566" t="n">
+        <v>-17.7</v>
+      </c>
+      <c r="L566" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="M566" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="N566" t="n">
+        <v>-12.5</v>
       </c>
     </row>
     <row r="567">
@@ -52839,43 +52958,43 @@
       <c r="A563" s="1" t="n">
         <v>46322</v>
       </c>
-      <c r="B563" t="n">
+      <c r="B563" s="0" t="n">
         <v>3.9</v>
       </c>
-      <c r="C563" t="n">
+      <c r="C563" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="D563" t="n">
+      <c r="D563" s="0" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="E563" t="n">
+      <c r="E563" s="0" t="n">
         <v>-8</v>
       </c>
-      <c r="F563" t="n">
+      <c r="F563" s="0" t="n">
         <v>-9.5</v>
       </c>
-      <c r="G563" t="n">
+      <c r="G563" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="H563" t="n">
+      <c r="H563" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="I563" t="n">
+      <c r="I563" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="J563" t="n">
+      <c r="J563" s="0" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="K563" t="n">
+      <c r="K563" s="0" t="n">
         <v>-5.6</v>
       </c>
-      <c r="L563" t="n">
+      <c r="L563" s="0" t="n">
         <v>-7.4</v>
       </c>
-      <c r="M563" t="n">
+      <c r="M563" s="0" t="n">
         <v>-6.1</v>
       </c>
-      <c r="N563" t="n">
+      <c r="N563" s="0" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -52883,15 +53002,134 @@
       <c r="A564" s="1" t="n">
         <v>46323</v>
       </c>
+      <c r="B564" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C564" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D564" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="E564" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F564" s="0" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="G564" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H564" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I564" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J564" s="0" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="K564" s="0" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="L564" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M564" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N564" s="0" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="1" t="n">
         <v>46324</v>
       </c>
+      <c r="B565" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="C565" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D565" s="0" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E565" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F565" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G565" s="0" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H565" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I565" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J565" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K565" s="0" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L565" s="0" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M565" s="0" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N565" s="0" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="1" t="n">
         <v>46325</v>
+      </c>
+      <c r="B566" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C566" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D566" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E566" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F566" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H566" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="I566" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J566" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="K566" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L566" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M566" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N566" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="567">
@@ -70645,51 +70883,51 @@
       <c r="A321" s="1" t="n">
         <v>46322</v>
       </c>
-      <c r="B321" t="n">
+      <c r="B321" s="0" t="n">
         <v>-4.93</v>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F321" t="n">
+      <c r="C321" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D321" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E321" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F321" s="0" t="n">
         <v>-18.13</v>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H321" t="n">
+      <c r="G321" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H321" s="0" t="n">
         <v>-7.15</v>
       </c>
-      <c r="I321" t="n">
+      <c r="I321" s="0" t="n">
         <v>-4.01</v>
       </c>
-      <c r="J321" t="n">
+      <c r="J321" s="0" t="n">
         <v>-16.28</v>
       </c>
-      <c r="K321" t="n">
+      <c r="K321" s="0" t="n">
         <v>-16.45</v>
       </c>
-      <c r="L321" t="n">
+      <c r="L321" s="0" t="n">
         <v>-14.75</v>
       </c>
-      <c r="M321" t="n">
+      <c r="M321" s="0" t="n">
         <v>-13.75</v>
       </c>
-      <c r="N321" t="n">
+      <c r="N321" s="0" t="n">
         <v>-6</v>
       </c>
     </row>
@@ -70697,15 +70935,156 @@
       <c r="A322" s="1" t="n">
         <v>46323</v>
       </c>
+      <c r="B322" s="0" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C322" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D322" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E322" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F322" s="0" t="n">
+        <v>-12.88</v>
+      </c>
+      <c r="G322" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H322" s="0" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="I322" s="0" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="J322" s="0" t="n">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="K322" s="0" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="L322" s="0" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="M322" s="0" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="N322" s="0" t="n">
+        <v>-3.6</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
         <v>46324</v>
       </c>
+      <c r="B323" s="0" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="C323" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D323" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E323" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F323" s="0" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="G323" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H323" s="0" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="I323" s="0" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="J323" s="0" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="K323" s="0" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="L323" s="0" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="M323" s="0" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="N323" s="0" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
         <v>46325</v>
+      </c>
+      <c r="B324" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>-11.11</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="I324" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="J324" t="n">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="K324" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="L324" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="M324" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="N324" t="n">
+        <v>-6.35</v>
       </c>
     </row>
     <row r="325">
